--- a/BOM E-MU SP-1200.xlsx
+++ b/BOM E-MU SP-1200.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="541">
   <si>
     <t>Checklist</t>
   </si>
@@ -327,7 +327,7 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
       <t>https://www.ebay.nl/itm/124591812891?hash=item1d0240311b:g:hhQAAOSwKThgNhUA</t>
     </r>
@@ -388,39 +388,6 @@
   </si>
   <si>
     <t>700-MX7523JN</t>
-  </si>
-  <si>
-    <t>II 304</t>
-  </si>
-  <si>
-    <t>ADC 0809</t>
-  </si>
-  <si>
-    <t>926-ADC0809CCVX/NOPB</t>
-  </si>
-  <si>
-    <t>II 336</t>
-  </si>
-  <si>
-    <t>7541 12 Bit MDAC</t>
-  </si>
-  <si>
-    <t>584-AD7541AJNZ</t>
-  </si>
-  <si>
-    <t>II 337</t>
-  </si>
-  <si>
-    <t>LF 398 S/H</t>
-  </si>
-  <si>
-    <t>926-LF398N/NOPB</t>
-  </si>
-  <si>
-    <t>II 338</t>
-  </si>
-  <si>
-    <t>2114 SRAM 4K 300 nS</t>
   </si>
   <si>
     <r>
@@ -428,19 +395,43 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.com/itm/283869354793?hash=item4217ee9b29:g:DoAAAOSwoA5dVDuM</t>
+      <t>https://www.eprelectronics.com/store/E-mu-Drum-machine-Command-Station-PARTS/E-mu-SP-1200-Sampling-Percussion-Model-7030-/IC-MDAC-AD7523-p62.html</t>
     </r>
   </si>
   <si>
-    <t>IM 357</t>
-  </si>
-  <si>
-    <t>Memory ICs and PALs</t>
-  </si>
-  <si>
-    <t>4464 64K x 4 RAM</t>
+    <t>II 304</t>
+  </si>
+  <si>
+    <t>ADC 0809</t>
+  </si>
+  <si>
+    <t>926-ADC0809CCVX/NOPB</t>
+  </si>
+  <si>
+    <t>II 336</t>
+  </si>
+  <si>
+    <t>7541 12 Bit MDAC</t>
+  </si>
+  <si>
+    <t>584-AD7541AJNZ</t>
+  </si>
+  <si>
+    <t>II 337</t>
+  </si>
+  <si>
+    <t>LF 398 S/H</t>
+  </si>
+  <si>
+    <t>926-LF398N/NOPB</t>
+  </si>
+  <si>
+    <t>II 338</t>
+  </si>
+  <si>
+    <t>2114 SRAM 4K 300 nS</t>
   </si>
   <si>
     <r>
@@ -448,28 +439,19 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.nl/itm/333851303960?hash=item4dbb16a018:g:cqkAAOSwgVZfdfXU</t>
+      <t>https://www.ebay.com/itm/283869354793?hash=item4217ee9b29:g:DoAAAOSwoA5dVDuM</t>
     </r>
   </si>
   <si>
-    <t>IM 373</t>
-  </si>
-  <si>
-    <t>74S288 i.LC PROM</t>
-  </si>
-  <si>
-    <t>IP 326</t>
-  </si>
-  <si>
-    <t>74S288 Log PROM</t>
-  </si>
-  <si>
-    <t>IP 327</t>
-  </si>
-  <si>
-    <t>Z-80 RAM PAL (PAL12H6)</t>
+    <t>IM 357</t>
+  </si>
+  <si>
+    <t>Memory ICs and PALs</t>
+  </si>
+  <si>
+    <t>4464 64K x 4 RAM</t>
   </si>
   <si>
     <r>
@@ -477,22 +459,28 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.com/itm/133263821487?hash=item1f07248aaf:g:vTYAAOSw2h1d6pzg</t>
+      <t>https://www.ebay.nl/itm/333851303960?hash=item4dbb16a018:g:cqkAAOSwgVZfdfXU</t>
     </r>
   </si>
   <si>
-    <t>IP 357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chip Select PAL (PAL16R4) </t>
-  </si>
-  <si>
-    <t>IP 358</t>
-  </si>
-  <si>
-    <t>Sound Mem. PAL(PAL16R8)</t>
+    <t>IM 373</t>
+  </si>
+  <si>
+    <t>74S288 uC PROM</t>
+  </si>
+  <si>
+    <t>IP 326</t>
+  </si>
+  <si>
+    <t>74S288 Log PROM</t>
+  </si>
+  <si>
+    <t>IP 327</t>
+  </si>
+  <si>
+    <t>Z-80 RAM PAL (PAL12H6)</t>
   </si>
   <si>
     <r>
@@ -500,25 +488,13 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.com/itm/133266092659?hash=item1f07473273:g:6~QAAOSwczxd7VLI</t>
+      <t>https://syntaur.com/Part-6666-ic-e-mu-ip357-sp1200-z80-ram-pal</t>
     </r>
   </si>
   <si>
-    <t>IP 359</t>
-  </si>
-  <si>
-    <t>IC69</t>
-  </si>
-  <si>
-    <t>DRAM PAL (PAL12L6)</t>
-  </si>
-  <si>
-    <t>IP 360</t>
-  </si>
-  <si>
-    <t>2764 Mainboot EPROM</t>
+    <t>IP 357</t>
   </si>
   <si>
     <r>
@@ -526,34 +502,13 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.nl/itm/164312001976?hash=item2641c22db8:g:JlsAAOSwZxNfAY7L</t>
+      <t>https://www.ebay.nl/sch/i.html?_nkw=PAL12H6CN+&amp;_sacat=0&amp;_from=R40&amp;_trksid=m570.l1313</t>
     </r>
   </si>
   <si>
-    <t>IP 362</t>
-  </si>
-  <si>
-    <t>4070 Quad XOR</t>
-  </si>
-  <si>
-    <t>595-CD4070BE</t>
-  </si>
-  <si>
-    <t>IC 131</t>
-  </si>
-  <si>
-    <t>Digital ICs</t>
-  </si>
-  <si>
-    <t>74C2 Tri-State Buffer</t>
-  </si>
-  <si>
-    <t>IC 341</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Z-80A CPU</t>
+    <t xml:space="preserve">Chip Select PAL (PAL16R4) </t>
   </si>
   <si>
     <r>
@@ -561,16 +516,22 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.budgetronics.eu/nl/ics/microcontrollers/z80a-cpu/a-10778-10000143</t>
+      <t>https://syntaur.com/Part-6797-ic-e-mu-ip358-sp-1200-chip-select-pal</t>
     </r>
   </si>
   <si>
-    <t>IM 343</t>
-  </si>
-  <si>
-    <t>Z-80A SIO/2</t>
+    <t>IP 358</t>
+  </si>
+  <si>
+    <t>Sound Mem. PAL(PAL16R8)</t>
+  </si>
+  <si>
+    <t>https://syntaur.com/Part-6803-ic-e-mu-ip359-sp1200-sound-memory-pal</t>
+  </si>
+  <si>
+    <t>IP 359</t>
   </si>
   <si>
     <r>
@@ -578,16 +539,25 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
-      <t>https://www.ebay.com/itm/224418751517</t>
+      <t>https://www.ebay.com/itm/133266092659?hash=item1f07473273:g:6~QAAOSwczxd7VLI</t>
     </r>
   </si>
   <si>
-    <t>IM 344</t>
-  </si>
-  <si>
-    <t>Z-80A Counter/Timer</t>
+    <t>IC69</t>
+  </si>
+  <si>
+    <t>DRAM PAL (PAL12L6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://syntaur.com/Part-7102-ic-e-mu-ip360-sp-1200-dram-pal</t>
+  </si>
+  <si>
+    <t>IP 360</t>
+  </si>
+  <si>
+    <t>2764 Mainboot EPROM</t>
   </si>
   <si>
     <r>
@@ -595,7 +565,76 @@
         <u val="single"/>
         <sz val="10"/>
         <color indexed="8"/>
-        <rFont val="Avenir Next"/>
+        <rFont val="Avenir Next Regular"/>
+      </rPr>
+      <t>https://www.ebay.nl/itm/164312001976?hash=item2641c22db8:g:JlsAAOSwZxNfAY7L</t>
+    </r>
+  </si>
+  <si>
+    <t>IP 362</t>
+  </si>
+  <si>
+    <t>4070 Quad XOR</t>
+  </si>
+  <si>
+    <t>595-CD4070BE</t>
+  </si>
+  <si>
+    <t>IC 131</t>
+  </si>
+  <si>
+    <t>Digital ICs</t>
+  </si>
+  <si>
+    <t>74C2 Tri-State Buffer</t>
+  </si>
+  <si>
+    <t>IC 341</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Z-80A CPU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Avenir Next Regular"/>
+      </rPr>
+      <t>https://www.budgetronics.eu/nl/ics/microcontrollers/z80a-cpu/a-10778-10000143</t>
+    </r>
+  </si>
+  <si>
+    <t>IM 343</t>
+  </si>
+  <si>
+    <t>Z-80A SIO/2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Avenir Next Regular"/>
+      </rPr>
+      <t>https://www.ebay.com/itm/224418751517</t>
+    </r>
+  </si>
+  <si>
+    <t>IM 344</t>
+  </si>
+  <si>
+    <t>Z-80A Counter/Timer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Avenir Next Regular"/>
       </rPr>
       <t>https://www.ebay.com/itm/353533557328?hash=item52503dfa50:g:yRoAAOSw919gxnee</t>
     </r>
@@ -760,10 +799,27 @@
     <t xml:space="preserve">74HCT157 Quad Mux </t>
   </si>
   <si>
+    <t>SN74HCT157N</t>
+  </si>
+  <si>
     <t>IT 379</t>
   </si>
   <si>
     <t>74HCT504</t>
+  </si>
+  <si>
+    <t>AM25L04DC</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Avenir Next Regular"/>
+      </rPr>
+      <t>https://www.ebay.nl/itm/225089491745?hash=item3468611321:g:UCkAAOSwmLlX2BrS&amp;amdata=enc:AQAIAAAA4MXkkTgkr469mE2jv47jaZSFkmu1KXiQnX/Nso3mcPS97IzzypAk0H+o9rlIYDpmkjyBVGYOWBtZtoT+BdeHSUU6AGFDY3SfO/YE5PuEZfCLTM4odbubofQn0JgDGTHJC6/TlEpXOjxiXHQ0OqXJztKbwwp+TFjcAtefcxbLPRNhiOoebneGfvAvEsmtcfkoqWswQudfCdiVs+C5iNOrlAA634r3DxrBAWRFFXCnr1TsvKrWbRQ36GYl1kbaPU04P1jLsqCYglIlL0cKuBR4R9uCn02Mzmm5JRSdt5+aJNYf|tkp:BFBM0oLsq9Vi</t>
+    </r>
   </si>
   <si>
     <t>IT 381</t>
@@ -1691,11 +1747,11 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Avenir Next"/>
+      <name val="Avenir Next Regular"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1727,12 +1783,18 @@
       <u val="single"/>
       <sz val="10"/>
       <color indexed="8"/>
-      <name val="Avenir Next"/>
+      <name val="Avenir Next Regular"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="16"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+      <color indexed="15"/>
+      <name val="Helvetica Neue"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1974,19 +2036,19 @@
     <xf numFmtId="49" fontId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -2292,7 +2354,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1200" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2322,7 +2383,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2348,7 +2408,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2374,7 +2433,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2400,7 +2458,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2426,7 +2483,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2452,7 +2508,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2478,7 +2533,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2504,7 +2558,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2530,7 +2583,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2585,7 +2637,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2611,7 +2662,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2637,7 +2687,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2663,7 +2712,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2689,7 +2737,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2715,7 +2762,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2741,7 +2787,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2767,7 +2812,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2793,7 +2837,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2819,7 +2862,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2867,7 +2909,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1000" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2877,10 +2918,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Avenir Next"/>
-            <a:ea typeface="Avenir Next"/>
-            <a:cs typeface="Avenir Next"/>
-            <a:sym typeface="Avenir Next"/>
+            <a:latin typeface="Avenir Next Regular"/>
+            <a:ea typeface="Avenir Next Regular"/>
+            <a:cs typeface="Avenir Next Regular"/>
+            <a:sym typeface="Avenir Next Regular"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2897,7 +2938,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2923,7 +2963,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2949,7 +2988,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -2975,7 +3013,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3001,7 +3038,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3027,7 +3063,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3053,7 +3088,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3079,7 +3113,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3105,7 +3138,6 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
           <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
             <a:ln>
               <a:noFill/>
@@ -3131,7 +3163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:K244"/>
+  <dimension ref="A2:L244"/>
   <sheetFormatPr defaultColWidth="8.17169" defaultRowHeight="21.65" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.17969" style="1" customWidth="1"/>
@@ -3142,8 +3174,8 @@
     <col min="7" max="7" width="11.6719" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.46094" style="1" customWidth="1"/>
     <col min="9" max="10" width="12.6484" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22.25" style="1" customWidth="1"/>
-    <col min="12" max="256" width="8.17969" style="1" customWidth="1"/>
+    <col min="11" max="12" width="22.25" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.17969" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3160,6 +3192,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" ht="22.6" customHeight="1">
       <c r="A2" s="3"/>
@@ -3187,6 +3220,7 @@
         <v>7</v>
       </c>
       <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" ht="22.85" customHeight="1">
       <c r="A3" t="b" s="4">
@@ -3211,7 +3245,8 @@
       <c r="J3" t="s" s="6">
         <v>11</v>
       </c>
-      <c r="K3" s="8"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" ht="22.75" customHeight="1">
       <c r="A4" t="b" s="9">
@@ -3236,7 +3271,8 @@
       <c r="J4" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K4" s="13"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="13"/>
     </row>
     <row r="5" ht="22.75" customHeight="1">
       <c r="A5" t="b" s="14">
@@ -3261,7 +3297,8 @@
       <c r="J5" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K5" s="18"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" ht="22.75" customHeight="1">
       <c r="A6" t="b" s="9">
@@ -3286,7 +3323,8 @@
       <c r="J6" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K6" s="13"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="13"/>
     </row>
     <row r="7" ht="22.75" customHeight="1">
       <c r="A7" t="b" s="14">
@@ -3311,7 +3349,8 @@
       <c r="J7" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="18"/>
     </row>
     <row r="8" ht="22.75" customHeight="1">
       <c r="A8" t="b" s="9">
@@ -3336,7 +3375,8 @@
       <c r="J8" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K8" s="13"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="13"/>
     </row>
     <row r="9" ht="22.75" customHeight="1">
       <c r="A9" t="b" s="14">
@@ -3361,7 +3401,8 @@
       <c r="J9" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K9" s="18"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" ht="22.75" customHeight="1">
       <c r="A10" t="b" s="9">
@@ -3386,7 +3427,8 @@
       <c r="J10" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="13"/>
     </row>
     <row r="11" ht="22.75" customHeight="1">
       <c r="A11" t="b" s="14">
@@ -3411,7 +3453,8 @@
       <c r="J11" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K11" s="18"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" ht="22.75" customHeight="1">
       <c r="A12" t="b" s="9">
@@ -3436,7 +3479,8 @@
       <c r="J12" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K12" s="13"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="13"/>
     </row>
     <row r="13" ht="22.75" customHeight="1">
       <c r="A13" t="b" s="14">
@@ -3461,7 +3505,8 @@
       <c r="J13" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K13" s="18"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" ht="22.75" customHeight="1">
       <c r="A14" t="b" s="9">
@@ -3486,7 +3531,8 @@
       <c r="J14" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K14" s="13"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="13"/>
     </row>
     <row r="15" ht="22.75" customHeight="1">
       <c r="A15" t="b" s="14">
@@ -3511,7 +3557,8 @@
       <c r="J15" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K15" s="18"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" ht="22.75" customHeight="1">
       <c r="A16" t="b" s="9">
@@ -3536,7 +3583,8 @@
       <c r="J16" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K16" s="13"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="13"/>
     </row>
     <row r="17" ht="22.75" customHeight="1">
       <c r="A17" t="b" s="14">
@@ -3561,7 +3609,8 @@
       <c r="J17" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K17" s="18"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" ht="22.75" customHeight="1">
       <c r="A18" t="b" s="9">
@@ -3586,7 +3635,8 @@
       <c r="J18" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K18" s="13"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="13"/>
     </row>
     <row r="19" ht="22.75" customHeight="1">
       <c r="A19" t="b" s="14">
@@ -3611,7 +3661,8 @@
       <c r="J19" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K19" s="18"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" ht="22.75" customHeight="1">
       <c r="A20" t="b" s="9">
@@ -3636,7 +3687,8 @@
       <c r="J20" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K20" s="13"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="13"/>
     </row>
     <row r="21" ht="22.75" customHeight="1">
       <c r="A21" t="b" s="14">
@@ -3661,7 +3713,8 @@
       <c r="J21" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K21" s="18"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" ht="22.75" customHeight="1">
       <c r="A22" t="b" s="9">
@@ -3686,7 +3739,8 @@
       <c r="J22" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K22" s="13"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="13"/>
     </row>
     <row r="23" ht="22.75" customHeight="1">
       <c r="A23" t="b" s="14">
@@ -3711,7 +3765,8 @@
       <c r="J23" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K23" s="18"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" ht="22.75" customHeight="1">
       <c r="A24" t="b" s="9">
@@ -3736,7 +3791,8 @@
       <c r="J24" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K24" s="13"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="13"/>
     </row>
     <row r="25" ht="22.75" customHeight="1">
       <c r="A25" t="b" s="14">
@@ -3761,7 +3817,8 @@
       <c r="J25" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K25" s="18"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="18"/>
     </row>
     <row r="26" ht="22.75" customHeight="1">
       <c r="A26" t="b" s="9">
@@ -3786,7 +3843,8 @@
       <c r="J26" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K26" s="13"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="13"/>
     </row>
     <row r="27" ht="22.75" customHeight="1">
       <c r="A27" t="b" s="14">
@@ -3811,7 +3869,8 @@
       <c r="J27" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K27" s="18"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="18"/>
     </row>
     <row r="28" ht="22.75" customHeight="1">
       <c r="A28" t="b" s="9">
@@ -3836,7 +3895,8 @@
       <c r="J28" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K28" s="13"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="13"/>
     </row>
     <row r="29" ht="22.75" customHeight="1">
       <c r="A29" t="b" s="14">
@@ -3861,7 +3921,8 @@
       <c r="J29" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K29" s="18"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="18"/>
     </row>
     <row r="30" ht="22.75" customHeight="1">
       <c r="A30" t="b" s="9">
@@ -3886,7 +3947,8 @@
       <c r="J30" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K30" s="13"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="13"/>
     </row>
     <row r="31" ht="22.75" customHeight="1">
       <c r="A31" t="b" s="14">
@@ -3911,7 +3973,8 @@
       <c r="J31" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K31" s="18"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="18"/>
     </row>
     <row r="32" ht="22.75" customHeight="1">
       <c r="A32" t="b" s="9">
@@ -3936,7 +3999,8 @@
       <c r="J32" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K32" s="13"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="13"/>
     </row>
     <row r="33" ht="22.75" customHeight="1">
       <c r="A33" t="b" s="14">
@@ -3961,7 +4025,8 @@
       <c r="J33" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K33" s="18"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="18"/>
     </row>
     <row r="34" ht="22.75" customHeight="1">
       <c r="A34" t="b" s="9">
@@ -3986,7 +4051,8 @@
       <c r="J34" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K34" s="13"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="13"/>
     </row>
     <row r="35" ht="22.75" customHeight="1">
       <c r="A35" t="b" s="14">
@@ -4011,7 +4077,8 @@
       <c r="J35" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K35" s="18"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="18"/>
     </row>
     <row r="36" ht="22.75" customHeight="1">
       <c r="A36" t="b" s="9">
@@ -4036,7 +4103,8 @@
       <c r="J36" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K36" s="13"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="13"/>
     </row>
     <row r="37" ht="22.75" customHeight="1">
       <c r="A37" t="b" s="14">
@@ -4061,7 +4129,8 @@
       <c r="J37" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K37" s="18"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="18"/>
     </row>
     <row r="38" ht="22.75" customHeight="1">
       <c r="A38" t="b" s="9">
@@ -4086,7 +4155,8 @@
       <c r="J38" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K38" s="13"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="13"/>
     </row>
     <row r="39" ht="50.35" customHeight="1">
       <c r="A39" t="b" s="14">
@@ -4113,9 +4183,10 @@
       <c r="J39" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K39" t="s" s="20">
+      <c r="K39" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L39" s="18"/>
     </row>
     <row r="40" ht="38.3" customHeight="1">
       <c r="A40" t="b" s="9">
@@ -4126,7 +4197,7 @@
       <c r="D40" t="s" s="11">
         <v>87</v>
       </c>
-      <c r="E40" t="s" s="21">
+      <c r="E40" t="s" s="20">
         <v>88</v>
       </c>
       <c r="F40" s="10"/>
@@ -4142,9 +4213,10 @@
       <c r="J40" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K40" t="s" s="22">
+      <c r="K40" t="s" s="11">
         <v>86</v>
       </c>
+      <c r="L40" s="13"/>
     </row>
     <row r="41" ht="22.75" customHeight="1">
       <c r="A41" t="b" s="14">
@@ -4171,9 +4243,10 @@
       <c r="J41" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K41" t="s" s="20">
+      <c r="K41" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L41" s="18"/>
     </row>
     <row r="42" ht="36.35" customHeight="1">
       <c r="A42" t="b" s="9">
@@ -4184,7 +4257,7 @@
       <c r="D42" t="s" s="11">
         <v>93</v>
       </c>
-      <c r="E42" t="s" s="23">
+      <c r="E42" t="s" s="21">
         <v>94</v>
       </c>
       <c r="F42" s="10"/>
@@ -4200,9 +4273,10 @@
       <c r="J42" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K42" t="s" s="22">
+      <c r="K42" t="s" s="11">
         <v>86</v>
       </c>
+      <c r="L42" s="13"/>
     </row>
     <row r="43" ht="22.75" customHeight="1">
       <c r="A43" t="b" s="14">
@@ -4229,9 +4303,10 @@
       <c r="J43" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K43" t="s" s="20">
+      <c r="K43" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L43" s="18"/>
     </row>
     <row r="44" ht="22.75" customHeight="1">
       <c r="A44" t="b" s="9">
@@ -4242,7 +4317,7 @@
       <c r="D44" t="s" s="11">
         <v>99</v>
       </c>
-      <c r="E44" t="s" s="23">
+      <c r="E44" t="s" s="21">
         <v>100</v>
       </c>
       <c r="F44" s="10"/>
@@ -4258,9 +4333,10 @@
       <c r="J44" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K44" t="s" s="22">
+      <c r="K44" t="s" s="11">
         <v>86</v>
       </c>
+      <c r="L44" s="13"/>
     </row>
     <row r="45" ht="64.75" customHeight="1">
       <c r="A45" t="b" s="14">
@@ -4287,9 +4363,10 @@
       <c r="J45" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K45" t="s" s="20">
+      <c r="K45" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L45" s="18"/>
     </row>
     <row r="46" ht="36.35" customHeight="1">
       <c r="A46" t="b" s="9">
@@ -4300,7 +4377,7 @@
       <c r="D46" t="s" s="11">
         <v>105</v>
       </c>
-      <c r="E46" t="s" s="23">
+      <c r="E46" t="s" s="21">
         <v>106</v>
       </c>
       <c r="F46" s="10"/>
@@ -4316,9 +4393,10 @@
       <c r="J46" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K46" t="s" s="22">
+      <c r="K46" t="s" s="11">
         <v>86</v>
       </c>
+      <c r="L46" s="13"/>
     </row>
     <row r="47" ht="36.35" customHeight="1">
       <c r="A47" t="b" s="14">
@@ -4345,9 +4423,10 @@
       <c r="J47" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K47" t="s" s="20">
+      <c r="K47" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L47" s="18"/>
     </row>
     <row r="48" ht="50.35" customHeight="1">
       <c r="A48" t="b" s="9">
@@ -4358,7 +4437,7 @@
       <c r="D48" t="s" s="11">
         <v>111</v>
       </c>
-      <c r="E48" t="s" s="23">
+      <c r="E48" t="s" s="21">
         <v>112</v>
       </c>
       <c r="F48" s="10"/>
@@ -4374,9 +4453,10 @@
       <c r="J48" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K48" t="s" s="22">
+      <c r="K48" t="s" s="11">
         <v>86</v>
       </c>
+      <c r="L48" s="13"/>
     </row>
     <row r="49" ht="22.75" customHeight="1">
       <c r="A49" t="b" s="14">
@@ -4403,9 +4483,10 @@
       <c r="J49" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K49" t="s" s="20">
+      <c r="K49" t="s" s="16">
         <v>86</v>
       </c>
+      <c r="L49" s="18"/>
     </row>
     <row r="50" ht="22.75" customHeight="1">
       <c r="A50" t="b" s="9">
@@ -4432,11 +4513,12 @@
       <c r="J50" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K50" t="s" s="22">
+      <c r="K50" t="s" s="11">
         <v>120</v>
       </c>
-    </row>
-    <row r="51" ht="22.75" customHeight="1">
+      <c r="L50" s="13"/>
+    </row>
+    <row r="51" ht="78.75" customHeight="1">
       <c r="A51" t="b" s="14">
         <v>0</v>
       </c>
@@ -4448,9 +4530,11 @@
       <c r="E51" t="s" s="16">
         <v>122</v>
       </c>
-      <c r="F51" s="15"/>
+      <c r="F51" t="s" s="16">
+        <v>123</v>
+      </c>
       <c r="G51" t="s" s="16">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H51" s="17">
         <v>1</v>
@@ -4461,9 +4545,10 @@
       <c r="J51" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K51" t="s" s="20">
+      <c r="K51" t="s" s="16">
         <v>120</v>
       </c>
+      <c r="L51" s="18"/>
     </row>
     <row r="52" ht="36.75" customHeight="1">
       <c r="A52" t="b" s="9">
@@ -4472,14 +4557,14 @@
       <c r="B52" s="10"/>
       <c r="C52" s="10"/>
       <c r="D52" t="s" s="11">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E52" t="s" s="11">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" t="s" s="11">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H52" s="12">
         <v>1</v>
@@ -4490,9 +4575,10 @@
       <c r="J52" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K52" t="s" s="22">
+      <c r="K52" t="s" s="11">
         <v>120</v>
       </c>
+      <c r="L52" s="13"/>
     </row>
     <row r="53" ht="22.75" customHeight="1">
       <c r="A53" t="b" s="14">
@@ -4501,14 +4587,14 @@
       <c r="B53" s="15"/>
       <c r="C53" s="15"/>
       <c r="D53" t="s" s="16">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E53" t="s" s="19">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F53" s="15"/>
       <c r="G53" t="s" s="16">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H53" s="17">
         <v>1</v>
@@ -4519,9 +4605,10 @@
       <c r="J53" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K53" t="s" s="20">
+      <c r="K53" t="s" s="16">
         <v>120</v>
       </c>
+      <c r="L53" s="18"/>
     </row>
     <row r="54" ht="22.75" customHeight="1">
       <c r="A54" t="b" s="9">
@@ -4530,14 +4617,14 @@
       <c r="B54" s="10"/>
       <c r="C54" s="10"/>
       <c r="D54" t="s" s="11">
-        <v>130</v>
-      </c>
-      <c r="E54" t="s" s="23">
         <v>131</v>
+      </c>
+      <c r="E54" t="s" s="21">
+        <v>132</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" t="s" s="11">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H54" s="12">
         <v>1</v>
@@ -4548,9 +4635,10 @@
       <c r="J54" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K54" t="s" s="22">
+      <c r="K54" t="s" s="11">
         <v>120</v>
       </c>
+      <c r="L54" s="13"/>
     </row>
     <row r="55" ht="64.75" customHeight="1">
       <c r="A55" t="b" s="14">
@@ -4559,14 +4647,14 @@
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
       <c r="D55" t="s" s="16">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" t="s" s="16">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G55" t="s" s="16">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H55" s="17">
         <v>6</v>
@@ -4577,9 +4665,10 @@
       <c r="J55" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K55" t="s" s="20">
-        <v>136</v>
-      </c>
+      <c r="K55" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="L55" s="18"/>
     </row>
     <row r="56" ht="64.75" customHeight="1">
       <c r="A56" t="b" s="9">
@@ -4588,14 +4677,14 @@
       <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" t="s" s="11">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E56" s="10"/>
       <c r="F56" t="s" s="11">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G56" t="s" s="11">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H56" s="12">
         <v>14</v>
@@ -4606,9 +4695,10 @@
       <c r="J56" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K56" t="s" s="22">
-        <v>136</v>
-      </c>
+      <c r="K56" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="L56" s="13"/>
     </row>
     <row r="57" ht="22.75" customHeight="1">
       <c r="A57" t="b" s="14">
@@ -4617,12 +4707,12 @@
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
       <c r="D57" t="s" s="16">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="15"/>
       <c r="G57" t="s" s="16">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H57" s="17">
         <v>1</v>
@@ -4633,9 +4723,10 @@
       <c r="J57" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K57" t="s" s="20">
-        <v>136</v>
-      </c>
+      <c r="K57" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="L57" s="18"/>
     </row>
     <row r="58" ht="22.75" customHeight="1">
       <c r="A58" t="b" s="9">
@@ -4644,12 +4735,12 @@
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
       <c r="D58" t="s" s="11">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" t="s" s="11">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H58" s="12">
         <v>1</v>
@@ -4660,25 +4751,26 @@
       <c r="J58" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K58" t="s" s="22">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" ht="64.75" customHeight="1">
+      <c r="K58" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="L58" s="13"/>
+    </row>
+    <row r="59" ht="78.75" customHeight="1">
       <c r="A59" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
       <c r="D59" t="s" s="16">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" t="s" s="16">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G59" t="s" s="16">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H59" s="17">
         <v>1</v>
@@ -4689,23 +4781,28 @@
       <c r="J59" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K59" t="s" s="20">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="60" ht="22.75" customHeight="1">
+      <c r="K59" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="L59" t="s" s="22">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" ht="36.75" customHeight="1">
       <c r="A60" t="b" s="9">
         <v>0</v>
       </c>
       <c r="B60" s="10"/>
       <c r="C60" s="10"/>
       <c r="D60" t="s" s="11">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
+      <c r="F60" t="s" s="11">
+        <v>150</v>
+      </c>
       <c r="G60" t="s" s="11">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H60" s="12">
         <v>1</v>
@@ -4716,9 +4813,10 @@
       <c r="J60" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K60" t="s" s="22">
-        <v>136</v>
-      </c>
+      <c r="K60" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="L60" s="13"/>
     </row>
     <row r="61" ht="64.75" customHeight="1">
       <c r="A61" t="b" s="14">
@@ -4727,14 +4825,14 @@
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" t="s" s="16">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" t="s" s="16">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G61" t="s" s="16">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H61" s="17">
         <v>1</v>
@@ -4745,25 +4843,30 @@
       <c r="J61" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K61" t="s" s="20">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="62" ht="22.75" customHeight="1">
+      <c r="K61" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="L61" t="s" s="22">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" ht="36.75" customHeight="1">
       <c r="A62" t="b" s="9">
         <v>0</v>
       </c>
       <c r="B62" t="s" s="11">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" t="s" s="11">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
+      <c r="F62" t="s" s="11">
+        <v>158</v>
+      </c>
       <c r="G62" t="s" s="11">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H62" s="12">
         <v>1</v>
@@ -4774,9 +4877,10 @@
       <c r="J62" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K62" t="s" s="22">
-        <v>136</v>
-      </c>
+      <c r="K62" t="s" s="11">
+        <v>137</v>
+      </c>
+      <c r="L62" s="13"/>
     </row>
     <row r="63" ht="64.75" customHeight="1">
       <c r="A63" t="b" s="14">
@@ -4785,14 +4889,14 @@
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
       <c r="D63" t="s" s="16">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E63" s="15"/>
       <c r="F63" t="s" s="16">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G63" t="s" s="16">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="H63" s="17">
         <v>1</v>
@@ -4803,9 +4907,10 @@
       <c r="J63" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K63" t="s" s="20">
-        <v>136</v>
-      </c>
+      <c r="K63" t="s" s="16">
+        <v>137</v>
+      </c>
+      <c r="L63" s="18"/>
     </row>
     <row r="64" ht="22.75" customHeight="1">
       <c r="A64" t="b" s="9">
@@ -4814,14 +4919,14 @@
       <c r="B64" s="10"/>
       <c r="C64" s="10"/>
       <c r="D64" t="s" s="11">
-        <v>158</v>
-      </c>
-      <c r="E64" t="s" s="23">
-        <v>159</v>
+        <v>163</v>
+      </c>
+      <c r="E64" t="s" s="21">
+        <v>164</v>
       </c>
       <c r="F64" s="10"/>
       <c r="G64" t="s" s="11">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H64" s="12">
         <v>1</v>
@@ -4832,9 +4937,10 @@
       <c r="J64" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K64" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K64" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L64" s="13"/>
     </row>
     <row r="65" ht="22.75" customHeight="1">
       <c r="A65" t="b" s="14">
@@ -4843,12 +4949,12 @@
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
       <c r="D65" t="s" s="16">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E65" s="15"/>
       <c r="F65" s="15"/>
       <c r="G65" t="s" s="16">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="H65" s="17">
         <v>1</v>
@@ -4859,9 +4965,10 @@
       <c r="J65" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K65" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K65" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L65" s="18"/>
     </row>
     <row r="66" ht="50.75" customHeight="1">
       <c r="A66" t="b" s="9">
@@ -4870,14 +4977,14 @@
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
       <c r="D66" t="s" s="11">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E66" s="10"/>
       <c r="F66" t="s" s="11">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G66" t="s" s="11">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H66" s="12">
         <v>1</v>
@@ -4888,9 +4995,10 @@
       <c r="J66" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K66" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K66" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L66" s="13"/>
     </row>
     <row r="67" ht="36.75" customHeight="1">
       <c r="A67" t="b" s="14">
@@ -4899,14 +5007,14 @@
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
       <c r="D67" t="s" s="16">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E67" s="15"/>
       <c r="F67" t="s" s="16">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G67" t="s" s="16">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H67" s="17">
         <v>1</v>
@@ -4917,9 +5025,10 @@
       <c r="J67" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K67" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K67" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L67" s="18"/>
     </row>
     <row r="68" ht="64.75" customHeight="1">
       <c r="A68" t="b" s="9">
@@ -4928,14 +5037,14 @@
       <c r="B68" s="10"/>
       <c r="C68" s="10"/>
       <c r="D68" t="s" s="11">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E68" s="10"/>
       <c r="F68" t="s" s="11">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G68" t="s" s="11">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H68" s="12">
         <v>1</v>
@@ -4946,9 +5055,10 @@
       <c r="J68" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K68" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K68" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L68" s="13"/>
     </row>
     <row r="69" ht="22.75" customHeight="1">
       <c r="A69" t="b" s="14">
@@ -4957,12 +5067,12 @@
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
       <c r="D69" t="s" s="16">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="15"/>
       <c r="G69" t="s" s="16">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="H69" s="17">
         <v>1</v>
@@ -4973,27 +5083,28 @@
       <c r="J69" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K69" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K69" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L69" s="18"/>
     </row>
     <row r="70" ht="22.75" customHeight="1">
       <c r="A70" t="b" s="9">
         <v>0</v>
       </c>
       <c r="B70" t="s" s="11">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C70" t="s" s="11">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D70" t="s" s="11">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" t="s" s="11">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H70" s="12">
         <v>1</v>
@@ -5004,27 +5115,28 @@
       <c r="J70" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K70" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K70" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L70" s="13"/>
     </row>
     <row r="71" ht="22.75" customHeight="1">
       <c r="A71" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B71" t="s" s="16">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s" s="16">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D71" t="s" s="16">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E71" s="15"/>
       <c r="F71" s="15"/>
       <c r="G71" t="s" s="16">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H71" s="17">
         <v>1</v>
@@ -5035,9 +5147,10 @@
       <c r="J71" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K71" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K71" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L71" s="18"/>
     </row>
     <row r="72" ht="22.75" customHeight="1">
       <c r="A72" t="b" s="9">
@@ -5046,12 +5159,12 @@
       <c r="B72" s="10"/>
       <c r="C72" s="10"/>
       <c r="D72" t="s" s="11">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" t="s" s="11">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H72" s="12">
         <v>1</v>
@@ -5062,9 +5175,10 @@
       <c r="J72" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K72" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K72" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L72" s="13"/>
     </row>
     <row r="73" ht="22.75" customHeight="1">
       <c r="A73" t="b" s="14">
@@ -5073,14 +5187,14 @@
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
       <c r="D73" t="s" s="16">
-        <v>184</v>
-      </c>
-      <c r="E73" t="s" s="24">
-        <v>185</v>
+        <v>189</v>
+      </c>
+      <c r="E73" t="s" s="23">
+        <v>190</v>
       </c>
       <c r="F73" s="15"/>
       <c r="G73" t="s" s="16">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H73" s="17">
         <v>2</v>
@@ -5091,9 +5205,10 @@
       <c r="J73" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K73" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K73" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L73" s="18"/>
     </row>
     <row r="74" ht="22.75" customHeight="1">
       <c r="A74" t="b" s="9">
@@ -5102,12 +5217,12 @@
       <c r="B74" s="10"/>
       <c r="C74" s="10"/>
       <c r="D74" t="s" s="11">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" t="s" s="11">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H74" s="12">
         <v>6</v>
@@ -5118,27 +5233,28 @@
       <c r="J74" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K74" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K74" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L74" s="13"/>
     </row>
     <row r="75" ht="36.75" customHeight="1">
       <c r="A75" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B75" t="s" s="16">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s" s="16">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D75" t="s" s="16">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E75" s="15"/>
       <c r="F75" s="15"/>
       <c r="G75" t="s" s="16">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H75" s="17">
         <v>2</v>
@@ -5149,9 +5265,10 @@
       <c r="J75" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K75" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K75" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L75" s="18"/>
     </row>
     <row r="76" ht="22.75" customHeight="1">
       <c r="A76" t="b" s="9">
@@ -5160,12 +5277,12 @@
       <c r="B76" s="10"/>
       <c r="C76" s="10"/>
       <c r="D76" t="s" s="11">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" t="s" s="11">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="H76" s="12">
         <v>1</v>
@@ -5176,27 +5293,28 @@
       <c r="J76" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K76" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K76" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L76" s="13"/>
     </row>
     <row r="77" ht="22.75" customHeight="1">
       <c r="A77" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B77" t="s" s="16">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s" s="16">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D77" t="s" s="16">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E77" s="15"/>
       <c r="F77" s="15"/>
       <c r="G77" t="s" s="16">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H77" s="17">
         <v>3</v>
@@ -5207,9 +5325,10 @@
       <c r="J77" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K77" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K77" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L77" s="18"/>
     </row>
     <row r="78" ht="22.75" customHeight="1">
       <c r="A78" t="b" s="9">
@@ -5218,12 +5337,12 @@
       <c r="B78" s="10"/>
       <c r="C78" s="10"/>
       <c r="D78" t="s" s="11">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" t="s" s="11">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H78" s="12">
         <v>2</v>
@@ -5234,9 +5353,10 @@
       <c r="J78" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K78" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K78" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L78" s="13"/>
     </row>
     <row r="79" ht="22.75" customHeight="1">
       <c r="A79" t="b" s="14">
@@ -5245,12 +5365,12 @@
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
       <c r="D79" t="s" s="16">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E79" s="15"/>
       <c r="F79" s="15"/>
       <c r="G79" t="s" s="16">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H79" s="17">
         <v>2</v>
@@ -5261,9 +5381,10 @@
       <c r="J79" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K79" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K79" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L79" s="18"/>
     </row>
     <row r="80" ht="22.75" customHeight="1">
       <c r="A80" t="b" s="9">
@@ -5272,12 +5393,12 @@
       <c r="B80" s="10"/>
       <c r="C80" s="10"/>
       <c r="D80" t="s" s="11">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" t="s" s="11">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H80" s="12">
         <v>2</v>
@@ -5288,9 +5409,10 @@
       <c r="J80" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K80" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K80" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L80" s="13"/>
     </row>
     <row r="81" ht="22.75" customHeight="1">
       <c r="A81" t="b" s="14">
@@ -5299,12 +5421,12 @@
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" t="s" s="16">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E81" s="15"/>
       <c r="F81" s="15"/>
       <c r="G81" t="s" s="16">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H81" s="17">
         <v>3</v>
@@ -5315,9 +5437,10 @@
       <c r="J81" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K81" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K81" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L81" s="18"/>
     </row>
     <row r="82" ht="22.75" customHeight="1">
       <c r="A82" t="b" s="9">
@@ -5326,12 +5449,12 @@
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
       <c r="D82" t="s" s="11">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" t="s" s="11">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H82" s="12">
         <v>5</v>
@@ -5342,9 +5465,10 @@
       <c r="J82" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K82" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K82" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L82" s="13"/>
     </row>
     <row r="83" ht="22.75" customHeight="1">
       <c r="A83" t="b" s="14">
@@ -5353,12 +5477,12 @@
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
       <c r="D83" t="s" s="16">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E83" s="15"/>
       <c r="F83" s="15"/>
       <c r="G83" t="s" s="16">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H83" s="17">
         <v>1</v>
@@ -5369,9 +5493,10 @@
       <c r="J83" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K83" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K83" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L83" s="18"/>
     </row>
     <row r="84" ht="22.75" customHeight="1">
       <c r="A84" t="b" s="9">
@@ -5380,12 +5505,12 @@
       <c r="B84" s="10"/>
       <c r="C84" s="10"/>
       <c r="D84" t="s" s="11">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" t="s" s="11">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H84" s="12">
         <v>1</v>
@@ -5396,9 +5521,10 @@
       <c r="J84" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K84" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K84" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L84" s="13"/>
     </row>
     <row r="85" ht="22.75" customHeight="1">
       <c r="A85" t="b" s="14">
@@ -5407,12 +5533,12 @@
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
       <c r="D85" t="s" s="16">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
       <c r="G85" t="s" s="16">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H85" s="17">
         <v>1</v>
@@ -5423,9 +5549,10 @@
       <c r="J85" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K85" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K85" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L85" s="18"/>
     </row>
     <row r="86" ht="22.75" customHeight="1">
       <c r="A86" t="b" s="9">
@@ -5434,12 +5561,12 @@
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
       <c r="D86" t="s" s="11">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" t="s" s="11">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H86" s="12">
         <v>2</v>
@@ -5450,9 +5577,10 @@
       <c r="J86" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K86" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K86" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L86" s="13"/>
     </row>
     <row r="87" ht="22.75" customHeight="1">
       <c r="A87" t="b" s="14">
@@ -5461,12 +5589,12 @@
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
       <c r="D87" t="s" s="16">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E87" s="15"/>
       <c r="F87" s="15"/>
       <c r="G87" t="s" s="16">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H87" s="17">
         <v>1</v>
@@ -5477,9 +5605,10 @@
       <c r="J87" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K87" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K87" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L87" s="18"/>
     </row>
     <row r="88" ht="22.75" customHeight="1">
       <c r="A88" t="b" s="9">
@@ -5488,12 +5617,12 @@
       <c r="B88" s="10"/>
       <c r="C88" s="10"/>
       <c r="D88" t="s" s="11">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" t="s" s="11">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H88" s="12">
         <v>4</v>
@@ -5504,27 +5633,28 @@
       <c r="J88" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K88" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K88" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L88" s="13"/>
     </row>
     <row r="89" ht="22.75" customHeight="1">
       <c r="A89" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B89" t="s" s="16">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C89" t="s" s="16">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D89" t="s" s="16">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E89" s="15"/>
       <c r="F89" s="15"/>
       <c r="G89" t="s" s="16">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H89" s="17">
         <v>1</v>
@@ -5535,9 +5665,10 @@
       <c r="J89" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K89" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K89" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L89" s="18"/>
     </row>
     <row r="90" ht="22.75" customHeight="1">
       <c r="A90" t="b" s="9">
@@ -5546,12 +5677,12 @@
       <c r="B90" s="10"/>
       <c r="C90" s="10"/>
       <c r="D90" t="s" s="11">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" t="s" s="11">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H90" s="12">
         <v>1</v>
@@ -5562,9 +5693,10 @@
       <c r="J90" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K90" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K90" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L90" s="13"/>
     </row>
     <row r="91" ht="22.75" customHeight="1">
       <c r="A91" t="b" s="14">
@@ -5573,12 +5705,14 @@
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
       <c r="D91" t="s" s="16">
-        <v>224</v>
-      </c>
-      <c r="E91" s="15"/>
+        <v>229</v>
+      </c>
+      <c r="E91" t="s" s="23">
+        <v>230</v>
+      </c>
       <c r="F91" s="15"/>
       <c r="G91" t="s" s="16">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="H91" s="17">
         <v>7</v>
@@ -5589,23 +5723,28 @@
       <c r="J91" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K91" t="s" s="20">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="92" ht="22.75" customHeight="1">
+      <c r="K91" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L91" s="18"/>
+    </row>
+    <row r="92" ht="260.75" customHeight="1">
       <c r="A92" t="b" s="9">
         <v>0</v>
       </c>
       <c r="B92" s="10"/>
       <c r="C92" s="10"/>
       <c r="D92" t="s" s="11">
-        <v>226</v>
-      </c>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
+        <v>232</v>
+      </c>
+      <c r="E92" t="s" s="24">
+        <v>233</v>
+      </c>
+      <c r="F92" t="s" s="11">
+        <v>234</v>
+      </c>
       <c r="G92" t="s" s="11">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H92" s="12">
         <v>1</v>
@@ -5616,9 +5755,10 @@
       <c r="J92" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K92" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K92" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L92" s="13"/>
     </row>
     <row r="93" ht="22.75" customHeight="1">
       <c r="A93" t="b" s="14">
@@ -5627,12 +5767,12 @@
       <c r="B93" s="15"/>
       <c r="C93" s="15"/>
       <c r="D93" t="s" s="16">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="E93" s="15"/>
       <c r="F93" s="15"/>
       <c r="G93" t="s" s="16">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H93" s="17">
         <v>2</v>
@@ -5643,9 +5783,10 @@
       <c r="J93" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K93" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K93" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L93" s="18"/>
     </row>
     <row r="94" ht="22.75" customHeight="1">
       <c r="A94" t="b" s="9">
@@ -5654,12 +5795,12 @@
       <c r="B94" s="10"/>
       <c r="C94" s="10"/>
       <c r="D94" t="s" s="11">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" t="s" s="11">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="H94" s="12">
         <v>3</v>
@@ -5670,9 +5811,10 @@
       <c r="J94" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K94" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K94" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L94" s="13"/>
     </row>
     <row r="95" ht="22.75" customHeight="1">
       <c r="A95" t="b" s="14">
@@ -5681,12 +5823,12 @@
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
       <c r="D95" t="s" s="16">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E95" s="15"/>
       <c r="F95" s="15"/>
       <c r="G95" t="s" s="16">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="H95" s="17">
         <v>1</v>
@@ -5697,9 +5839,10 @@
       <c r="J95" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K95" t="s" s="20">
-        <v>161</v>
-      </c>
+      <c r="K95" t="s" s="16">
+        <v>166</v>
+      </c>
+      <c r="L95" s="18"/>
     </row>
     <row r="96" ht="22.75" customHeight="1">
       <c r="A96" t="b" s="9">
@@ -5708,12 +5851,12 @@
       <c r="B96" s="10"/>
       <c r="C96" s="10"/>
       <c r="D96" t="s" s="11">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" t="s" s="11">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H96" s="12">
         <v>2</v>
@@ -5724,9 +5867,10 @@
       <c r="J96" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K96" t="s" s="22">
-        <v>161</v>
-      </c>
+      <c r="K96" t="s" s="11">
+        <v>166</v>
+      </c>
+      <c r="L96" s="13"/>
     </row>
     <row r="97" ht="22.75" customHeight="1">
       <c r="A97" t="b" s="14">
@@ -5735,23 +5879,24 @@
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
       <c r="D97" t="s" s="16">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E97" s="15"/>
       <c r="F97" s="15"/>
       <c r="G97" t="s" s="16">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H97" s="17">
         <v>1</v>
       </c>
       <c r="I97" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J97" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K97" s="18"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="18"/>
     </row>
     <row r="98" ht="22.75" customHeight="1">
       <c r="A98" t="b" s="9">
@@ -5760,23 +5905,24 @@
       <c r="B98" s="10"/>
       <c r="C98" s="10"/>
       <c r="D98" t="s" s="11">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" t="s" s="11">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="H98" s="12">
         <v>2</v>
       </c>
       <c r="I98" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J98" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K98" s="13"/>
+      <c r="K98" s="10"/>
+      <c r="L98" s="13"/>
     </row>
     <row r="99" ht="22.75" customHeight="1">
       <c r="A99" t="b" s="14">
@@ -5785,23 +5931,24 @@
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" t="s" s="16">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E99" s="15"/>
       <c r="F99" s="15"/>
       <c r="G99" t="s" s="16">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H99" s="17">
         <v>1</v>
       </c>
       <c r="I99" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J99" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K99" s="18"/>
+      <c r="K99" s="15"/>
+      <c r="L99" s="18"/>
     </row>
     <row r="100" ht="22.75" customHeight="1">
       <c r="A100" t="b" s="9">
@@ -5810,23 +5957,24 @@
       <c r="B100" s="10"/>
       <c r="C100" s="10"/>
       <c r="D100" t="s" s="11">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" t="s" s="11">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H100" s="12">
         <v>7</v>
       </c>
       <c r="I100" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J100" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K100" s="13"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="13"/>
     </row>
     <row r="101" ht="22.75" customHeight="1">
       <c r="A101" t="b" s="14">
@@ -5835,23 +5983,24 @@
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
       <c r="D101" t="s" s="16">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="E101" s="15"/>
       <c r="F101" s="15"/>
       <c r="G101" t="s" s="16">
+        <v>254</v>
+      </c>
+      <c r="H101" s="17">
+        <v>1</v>
+      </c>
+      <c r="I101" t="s" s="16">
         <v>246</v>
       </c>
-      <c r="H101" s="17">
-        <v>1</v>
-      </c>
-      <c r="I101" t="s" s="16">
-        <v>238</v>
-      </c>
       <c r="J101" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K101" s="18"/>
+      <c r="K101" s="15"/>
+      <c r="L101" s="18"/>
     </row>
     <row r="102" ht="22.75" customHeight="1">
       <c r="A102" t="b" s="9">
@@ -5860,23 +6009,24 @@
       <c r="B102" s="10"/>
       <c r="C102" s="10"/>
       <c r="D102" t="s" s="11">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" t="s" s="11">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="H102" s="12">
         <v>1</v>
       </c>
       <c r="I102" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J102" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K102" s="13"/>
+      <c r="K102" s="10"/>
+      <c r="L102" s="13"/>
     </row>
     <row r="103" ht="22.75" customHeight="1">
       <c r="A103" t="b" s="14">
@@ -5885,23 +6035,24 @@
       <c r="B103" s="15"/>
       <c r="C103" s="15"/>
       <c r="D103" t="s" s="16">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="15"/>
       <c r="G103" t="s" s="16">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="H103" s="17">
         <v>1</v>
       </c>
       <c r="I103" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J103" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K103" s="18"/>
+      <c r="K103" s="15"/>
+      <c r="L103" s="18"/>
     </row>
     <row r="104" ht="22.75" customHeight="1">
       <c r="A104" t="b" s="9">
@@ -5910,23 +6061,24 @@
       <c r="B104" s="10"/>
       <c r="C104" s="10"/>
       <c r="D104" t="s" s="11">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" t="s" s="11">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="H104" s="12">
         <v>1</v>
       </c>
       <c r="I104" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J104" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K104" s="13"/>
+      <c r="K104" s="10"/>
+      <c r="L104" s="13"/>
     </row>
     <row r="105" ht="22.75" customHeight="1">
       <c r="A105" t="b" s="14">
@@ -5935,23 +6087,24 @@
       <c r="B105" s="15"/>
       <c r="C105" s="15"/>
       <c r="D105" t="s" s="16">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E105" s="15"/>
       <c r="F105" s="15"/>
       <c r="G105" t="s" s="16">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H105" s="17">
         <v>2</v>
       </c>
       <c r="I105" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J105" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K105" s="18"/>
+      <c r="K105" s="15"/>
+      <c r="L105" s="18"/>
     </row>
     <row r="106" ht="22.75" customHeight="1">
       <c r="A106" t="b" s="9">
@@ -5960,23 +6113,24 @@
       <c r="B106" s="10"/>
       <c r="C106" s="10"/>
       <c r="D106" t="s" s="11">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" t="s" s="11">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="H106" s="12">
         <v>1</v>
       </c>
       <c r="I106" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J106" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K106" s="13"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="13"/>
     </row>
     <row r="107" ht="22.75" customHeight="1">
       <c r="A107" t="b" s="14">
@@ -5985,23 +6139,24 @@
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
       <c r="D107" t="s" s="16">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E107" s="15"/>
       <c r="F107" s="15"/>
       <c r="G107" t="s" s="16">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="H107" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I107" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J107" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K107" s="18"/>
+      <c r="K107" s="15"/>
+      <c r="L107" s="18"/>
     </row>
     <row r="108" ht="22.75" customHeight="1">
       <c r="A108" t="b" s="9">
@@ -6010,23 +6165,24 @@
       <c r="B108" s="10"/>
       <c r="C108" s="10"/>
       <c r="D108" t="s" s="11">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" t="s" s="11">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="H108" t="s" s="11">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I108" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J108" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K108" s="13"/>
+      <c r="K108" s="10"/>
+      <c r="L108" s="13"/>
     </row>
     <row r="109" ht="22.75" customHeight="1">
       <c r="A109" t="b" s="14">
@@ -6035,23 +6191,24 @@
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
       <c r="D109" t="s" s="16">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E109" s="15"/>
       <c r="F109" s="15"/>
       <c r="G109" t="s" s="16">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H109" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I109" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J109" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K109" s="18"/>
+      <c r="K109" s="15"/>
+      <c r="L109" s="18"/>
     </row>
     <row r="110" ht="22.75" customHeight="1">
       <c r="A110" t="b" s="9">
@@ -6060,23 +6217,24 @@
       <c r="B110" s="10"/>
       <c r="C110" s="10"/>
       <c r="D110" t="s" s="11">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" t="s" s="11">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="H110" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I110" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J110" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K110" s="13"/>
+      <c r="K110" s="10"/>
+      <c r="L110" s="13"/>
     </row>
     <row r="111" ht="22.75" customHeight="1">
       <c r="A111" t="b" s="14">
@@ -6085,23 +6243,24 @@
       <c r="B111" s="15"/>
       <c r="C111" s="15"/>
       <c r="D111" t="s" s="16">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="E111" s="15"/>
       <c r="F111" s="15"/>
       <c r="G111" t="s" s="16">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="H111" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I111" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J111" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K111" s="18"/>
+      <c r="K111" s="15"/>
+      <c r="L111" s="18"/>
     </row>
     <row r="112" ht="22.75" customHeight="1">
       <c r="A112" t="b" s="9">
@@ -6110,23 +6269,24 @@
       <c r="B112" s="10"/>
       <c r="C112" s="10"/>
       <c r="D112" t="s" s="11">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" t="s" s="11">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="H112" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I112" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J112" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K112" s="13"/>
+      <c r="K112" s="10"/>
+      <c r="L112" s="13"/>
     </row>
     <row r="113" ht="22.75" customHeight="1">
       <c r="A113" t="b" s="14">
@@ -6135,23 +6295,24 @@
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
       <c r="D113" t="s" s="16">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="E113" s="15"/>
       <c r="F113" s="15"/>
       <c r="G113" t="s" s="16">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="H113" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I113" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J113" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K113" s="18"/>
+      <c r="K113" s="15"/>
+      <c r="L113" s="18"/>
     </row>
     <row r="114" ht="22.75" customHeight="1">
       <c r="A114" t="b" s="9">
@@ -6160,23 +6321,24 @@
       <c r="B114" s="10"/>
       <c r="C114" s="10"/>
       <c r="D114" t="s" s="11">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" t="s" s="11">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="H114" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I114" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J114" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K114" s="13"/>
+      <c r="K114" s="10"/>
+      <c r="L114" s="13"/>
     </row>
     <row r="115" ht="22.75" customHeight="1">
       <c r="A115" t="b" s="14">
@@ -6185,23 +6347,24 @@
       <c r="B115" s="15"/>
       <c r="C115" s="15"/>
       <c r="D115" t="s" s="16">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E115" s="15"/>
       <c r="F115" s="15"/>
       <c r="G115" t="s" s="16">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="H115" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I115" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J115" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K115" s="18"/>
+      <c r="K115" s="15"/>
+      <c r="L115" s="18"/>
     </row>
     <row r="116" ht="22.75" customHeight="1">
       <c r="A116" t="b" s="9">
@@ -6210,23 +6373,24 @@
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
       <c r="D116" t="s" s="11">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" t="s" s="11">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="H116" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I116" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J116" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K116" s="13"/>
+      <c r="K116" s="10"/>
+      <c r="L116" s="13"/>
     </row>
     <row r="117" ht="22.75" customHeight="1">
       <c r="A117" t="b" s="14">
@@ -6235,23 +6399,24 @@
       <c r="B117" s="15"/>
       <c r="C117" s="15"/>
       <c r="D117" t="s" s="16">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E117" s="15"/>
       <c r="F117" s="15"/>
       <c r="G117" t="s" s="16">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="H117" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I117" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J117" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K117" s="18"/>
+      <c r="K117" s="15"/>
+      <c r="L117" s="18"/>
     </row>
     <row r="118" ht="22.75" customHeight="1">
       <c r="A118" t="b" s="9">
@@ -6260,23 +6425,24 @@
       <c r="B118" s="10"/>
       <c r="C118" s="10"/>
       <c r="D118" t="s" s="11">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" t="s" s="11">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="H118" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I118" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J118" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K118" s="13"/>
+      <c r="K118" s="10"/>
+      <c r="L118" s="13"/>
     </row>
     <row r="119" ht="22.75" customHeight="1">
       <c r="A119" t="b" s="14">
@@ -6285,23 +6451,24 @@
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
       <c r="D119" t="s" s="16">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="E119" s="15"/>
       <c r="F119" s="15"/>
       <c r="G119" t="s" s="16">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="H119" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I119" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J119" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K119" s="18"/>
+      <c r="K119" s="15"/>
+      <c r="L119" s="18"/>
     </row>
     <row r="120" ht="22.75" customHeight="1">
       <c r="A120" t="b" s="9">
@@ -6310,23 +6477,24 @@
       <c r="B120" s="10"/>
       <c r="C120" s="10"/>
       <c r="D120" t="s" s="11">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" t="s" s="11">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="H120" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I120" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J120" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K120" s="13"/>
+      <c r="K120" s="10"/>
+      <c r="L120" s="13"/>
     </row>
     <row r="121" ht="22.75" customHeight="1">
       <c r="A121" t="b" s="14">
@@ -6335,23 +6503,24 @@
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
       <c r="D121" t="s" s="16">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="E121" s="15"/>
       <c r="F121" s="15"/>
       <c r="G121" t="s" s="16">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="H121" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I121" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J121" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K121" s="18"/>
+      <c r="K121" s="15"/>
+      <c r="L121" s="18"/>
     </row>
     <row r="122" ht="22.75" customHeight="1">
       <c r="A122" t="b" s="9">
@@ -6360,23 +6529,24 @@
       <c r="B122" s="10"/>
       <c r="C122" s="10"/>
       <c r="D122" t="s" s="11">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" t="s" s="11">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="H122" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I122" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J122" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K122" s="13"/>
+      <c r="K122" s="10"/>
+      <c r="L122" s="13"/>
     </row>
     <row r="123" ht="22.75" customHeight="1">
       <c r="A123" t="b" s="14">
@@ -6385,23 +6555,24 @@
       <c r="B123" s="15"/>
       <c r="C123" s="15"/>
       <c r="D123" t="s" s="16">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="E123" s="15"/>
       <c r="F123" s="15"/>
       <c r="G123" t="s" s="16">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="H123" t="s" s="16">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I123" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J123" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K123" s="18"/>
+      <c r="K123" s="15"/>
+      <c r="L123" s="18"/>
     </row>
     <row r="124" ht="22.75" customHeight="1">
       <c r="A124" t="b" s="9">
@@ -6410,23 +6581,24 @@
       <c r="B124" s="10"/>
       <c r="C124" s="10"/>
       <c r="D124" t="s" s="11">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" t="s" s="11">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="H124" t="s" s="11">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I124" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J124" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K124" s="13"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="13"/>
     </row>
     <row r="125" ht="22.75" customHeight="1">
       <c r="A125" t="b" s="14">
@@ -6435,23 +6607,24 @@
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
       <c r="D125" t="s" s="16">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="E125" s="15"/>
       <c r="F125" s="15"/>
       <c r="G125" t="s" s="16">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="H125" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I125" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J125" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K125" s="18"/>
+      <c r="K125" s="15"/>
+      <c r="L125" s="18"/>
     </row>
     <row r="126" ht="22.75" customHeight="1">
       <c r="A126" t="b" s="9">
@@ -6460,23 +6633,24 @@
       <c r="B126" s="10"/>
       <c r="C126" s="10"/>
       <c r="D126" t="s" s="11">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" t="s" s="11">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="H126" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I126" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J126" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K126" s="13"/>
+      <c r="K126" s="10"/>
+      <c r="L126" s="13"/>
     </row>
     <row r="127" ht="22.75" customHeight="1">
       <c r="A127" t="b" s="14">
@@ -6485,23 +6659,24 @@
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
       <c r="D127" t="s" s="16">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E127" s="15"/>
       <c r="F127" s="15"/>
       <c r="G127" t="s" s="16">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="H127" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I127" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J127" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K127" s="18"/>
+      <c r="K127" s="15"/>
+      <c r="L127" s="18"/>
     </row>
     <row r="128" ht="22.75" customHeight="1">
       <c r="A128" t="b" s="9">
@@ -6510,23 +6685,24 @@
       <c r="B128" s="10"/>
       <c r="C128" s="10"/>
       <c r="D128" t="s" s="11">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" t="s" s="11">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H128" t="s" s="11">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I128" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J128" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K128" s="13"/>
+      <c r="K128" s="10"/>
+      <c r="L128" s="13"/>
     </row>
     <row r="129" ht="22.75" customHeight="1">
       <c r="A129" t="b" s="14">
@@ -6535,23 +6711,24 @@
       <c r="B129" s="15"/>
       <c r="C129" s="15"/>
       <c r="D129" t="s" s="16">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="E129" s="15"/>
       <c r="F129" s="15"/>
       <c r="G129" t="s" s="16">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H129" t="s" s="16">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I129" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J129" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K129" s="18"/>
+      <c r="K129" s="15"/>
+      <c r="L129" s="18"/>
     </row>
     <row r="130" ht="22.75" customHeight="1">
       <c r="A130" t="b" s="9">
@@ -6560,23 +6737,24 @@
       <c r="B130" s="10"/>
       <c r="C130" s="10"/>
       <c r="D130" t="s" s="11">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" t="s" s="11">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="H130" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I130" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J130" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K130" s="13"/>
+      <c r="K130" s="10"/>
+      <c r="L130" s="13"/>
     </row>
     <row r="131" ht="22.75" customHeight="1">
       <c r="A131" t="b" s="14">
@@ -6585,23 +6763,24 @@
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
       <c r="D131" t="s" s="16">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="E131" s="15"/>
       <c r="F131" s="15"/>
       <c r="G131" t="s" s="16">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="H131" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I131" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J131" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K131" s="18"/>
+      <c r="K131" s="15"/>
+      <c r="L131" s="18"/>
     </row>
     <row r="132" ht="22.75" customHeight="1">
       <c r="A132" t="b" s="9">
@@ -6610,23 +6789,24 @@
       <c r="B132" s="10"/>
       <c r="C132" s="10"/>
       <c r="D132" t="s" s="11">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" t="s" s="11">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="H132" t="s" s="11">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="I132" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J132" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K132" s="13"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="13"/>
     </row>
     <row r="133" ht="22.75" customHeight="1">
       <c r="A133" t="b" s="14">
@@ -6635,23 +6815,24 @@
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
       <c r="D133" t="s" s="16">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E133" s="15"/>
       <c r="F133" s="15"/>
       <c r="G133" t="s" s="16">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="H133" t="s" s="16">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="I133" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J133" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K133" s="18"/>
+      <c r="K133" s="15"/>
+      <c r="L133" s="18"/>
     </row>
     <row r="134" ht="22.75" customHeight="1">
       <c r="A134" t="b" s="9">
@@ -6660,23 +6841,24 @@
       <c r="B134" s="10"/>
       <c r="C134" s="10"/>
       <c r="D134" t="s" s="11">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" t="s" s="11">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H134" t="s" s="11">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="I134" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J134" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K134" s="13"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="13"/>
     </row>
     <row r="135" ht="22.75" customHeight="1">
       <c r="A135" t="b" s="14">
@@ -6685,23 +6867,24 @@
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
       <c r="D135" t="s" s="16">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E135" s="15"/>
       <c r="F135" s="15"/>
       <c r="G135" t="s" s="16">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="H135" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I135" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J135" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K135" s="18"/>
+      <c r="K135" s="15"/>
+      <c r="L135" s="18"/>
     </row>
     <row r="136" ht="22.75" customHeight="1">
       <c r="A136" t="b" s="9">
@@ -6710,23 +6893,24 @@
       <c r="B136" s="10"/>
       <c r="C136" s="10"/>
       <c r="D136" t="s" s="11">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" t="s" s="11">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H136" t="s" s="11">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I136" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J136" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K136" s="13"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="13"/>
     </row>
     <row r="137" ht="22.75" customHeight="1">
       <c r="A137" t="b" s="14">
@@ -6735,23 +6919,24 @@
       <c r="B137" s="15"/>
       <c r="C137" s="15"/>
       <c r="D137" t="s" s="16">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E137" s="15"/>
       <c r="F137" s="15"/>
       <c r="G137" t="s" s="16">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H137" t="s" s="16">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="I137" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J137" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K137" s="18"/>
+      <c r="K137" s="15"/>
+      <c r="L137" s="18"/>
     </row>
     <row r="138" ht="22.75" customHeight="1">
       <c r="A138" t="b" s="9">
@@ -6760,23 +6945,24 @@
       <c r="B138" s="10"/>
       <c r="C138" s="10"/>
       <c r="D138" t="s" s="11">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" t="s" s="11">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H138" t="s" s="11">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I138" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J138" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K138" s="13"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="13"/>
     </row>
     <row r="139" ht="22.75" customHeight="1">
       <c r="A139" t="b" s="14">
@@ -6785,23 +6971,24 @@
       <c r="B139" s="15"/>
       <c r="C139" s="15"/>
       <c r="D139" t="s" s="16">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E139" s="15"/>
       <c r="F139" s="15"/>
       <c r="G139" t="s" s="16">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="H139" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I139" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J139" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K139" s="18"/>
+      <c r="K139" s="15"/>
+      <c r="L139" s="18"/>
     </row>
     <row r="140" ht="22.75" customHeight="1">
       <c r="A140" t="b" s="9">
@@ -6810,23 +6997,24 @@
       <c r="B140" s="10"/>
       <c r="C140" s="10"/>
       <c r="D140" t="s" s="11">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" t="s" s="11">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="H140" t="s" s="11">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I140" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J140" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K140" s="13"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="13"/>
     </row>
     <row r="141" ht="22.75" customHeight="1">
       <c r="A141" t="b" s="14">
@@ -6835,23 +7023,24 @@
       <c r="B141" s="15"/>
       <c r="C141" s="15"/>
       <c r="D141" t="s" s="16">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="E141" s="15"/>
       <c r="F141" s="15"/>
       <c r="G141" t="s" s="16">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="H141" t="s" s="16">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I141" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J141" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K141" s="18"/>
+      <c r="K141" s="15"/>
+      <c r="L141" s="18"/>
     </row>
     <row r="142" ht="22.75" customHeight="1">
       <c r="A142" t="b" s="9">
@@ -6860,23 +7049,24 @@
       <c r="B142" s="10"/>
       <c r="C142" s="10"/>
       <c r="D142" t="s" s="11">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" t="s" s="11">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="H142" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I142" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J142" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K142" s="13"/>
+      <c r="K142" s="10"/>
+      <c r="L142" s="13"/>
     </row>
     <row r="143" ht="22.75" customHeight="1">
       <c r="A143" t="b" s="14">
@@ -6885,23 +7075,24 @@
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
       <c r="D143" t="s" s="16">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E143" s="15"/>
       <c r="F143" s="15"/>
       <c r="G143" t="s" s="16">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="H143" t="s" s="16">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="I143" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J143" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K143" s="18"/>
+      <c r="K143" s="15"/>
+      <c r="L143" s="18"/>
     </row>
     <row r="144" ht="22.75" customHeight="1">
       <c r="A144" t="b" s="9">
@@ -6910,23 +7101,24 @@
       <c r="B144" s="10"/>
       <c r="C144" s="10"/>
       <c r="D144" t="s" s="11">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" t="s" s="11">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H144" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I144" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J144" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K144" s="13"/>
+      <c r="K144" s="10"/>
+      <c r="L144" s="13"/>
     </row>
     <row r="145" ht="22.75" customHeight="1">
       <c r="A145" t="b" s="14">
@@ -6935,23 +7127,24 @@
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
       <c r="D145" t="s" s="16">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="E145" s="15"/>
       <c r="F145" s="15"/>
       <c r="G145" t="s" s="16">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="H145" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I145" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J145" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K145" s="18"/>
+      <c r="K145" s="15"/>
+      <c r="L145" s="18"/>
     </row>
     <row r="146" ht="22.75" customHeight="1">
       <c r="A146" t="b" s="9">
@@ -6960,23 +7153,24 @@
       <c r="B146" s="10"/>
       <c r="C146" s="10"/>
       <c r="D146" t="s" s="11">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" t="s" s="11">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="H146" t="s" s="11">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="I146" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J146" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K146" s="13"/>
+      <c r="K146" s="10"/>
+      <c r="L146" s="13"/>
     </row>
     <row r="147" ht="22.75" customHeight="1">
       <c r="A147" t="b" s="14">
@@ -6985,23 +7179,24 @@
       <c r="B147" s="15"/>
       <c r="C147" s="15"/>
       <c r="D147" t="s" s="16">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="E147" s="15"/>
       <c r="F147" s="15"/>
       <c r="G147" t="s" s="16">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="H147" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I147" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J147" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K147" s="18"/>
+      <c r="K147" s="15"/>
+      <c r="L147" s="18"/>
     </row>
     <row r="148" ht="22.75" customHeight="1">
       <c r="A148" t="b" s="9">
@@ -7010,23 +7205,24 @@
       <c r="B148" s="10"/>
       <c r="C148" s="10"/>
       <c r="D148" t="s" s="11">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" t="s" s="11">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H148" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I148" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J148" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K148" s="13"/>
+      <c r="K148" s="10"/>
+      <c r="L148" s="13"/>
     </row>
     <row r="149" ht="22.75" customHeight="1">
       <c r="A149" t="b" s="14">
@@ -7035,23 +7231,24 @@
       <c r="B149" s="15"/>
       <c r="C149" s="15"/>
       <c r="D149" t="s" s="16">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="E149" s="15"/>
       <c r="F149" s="15"/>
       <c r="G149" t="s" s="16">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="H149" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I149" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J149" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K149" s="18"/>
+      <c r="K149" s="15"/>
+      <c r="L149" s="18"/>
     </row>
     <row r="150" ht="22.75" customHeight="1">
       <c r="A150" t="b" s="9">
@@ -7060,23 +7257,24 @@
       <c r="B150" s="10"/>
       <c r="C150" s="10"/>
       <c r="D150" t="s" s="11">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" t="s" s="11">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H150" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I150" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J150" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K150" s="13"/>
+      <c r="K150" s="10"/>
+      <c r="L150" s="13"/>
     </row>
     <row r="151" ht="22.75" customHeight="1">
       <c r="A151" t="b" s="14">
@@ -7085,23 +7283,24 @@
       <c r="B151" s="15"/>
       <c r="C151" s="15"/>
       <c r="D151" t="s" s="16">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="E151" s="15"/>
       <c r="F151" s="15"/>
       <c r="G151" t="s" s="16">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="H151" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I151" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J151" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K151" s="18"/>
+      <c r="K151" s="15"/>
+      <c r="L151" s="18"/>
     </row>
     <row r="152" ht="22.75" customHeight="1">
       <c r="A152" t="b" s="9">
@@ -7110,23 +7309,24 @@
       <c r="B152" s="10"/>
       <c r="C152" s="10"/>
       <c r="D152" t="s" s="11">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
       <c r="G152" t="s" s="11">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="H152" t="s" s="11">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I152" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J152" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K152" s="13"/>
+      <c r="K152" s="10"/>
+      <c r="L152" s="13"/>
     </row>
     <row r="153" ht="22.75" customHeight="1">
       <c r="A153" t="b" s="14">
@@ -7135,23 +7335,24 @@
       <c r="B153" s="15"/>
       <c r="C153" s="15"/>
       <c r="D153" t="s" s="16">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="E153" s="15"/>
       <c r="F153" s="15"/>
       <c r="G153" t="s" s="16">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H153" t="s" s="16">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I153" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J153" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K153" s="18"/>
+      <c r="K153" s="15"/>
+      <c r="L153" s="18"/>
     </row>
     <row r="154" ht="22.75" customHeight="1">
       <c r="A154" t="b" s="9">
@@ -7160,23 +7361,24 @@
       <c r="B154" s="10"/>
       <c r="C154" s="10"/>
       <c r="D154" t="s" s="11">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
       <c r="G154" t="s" s="11">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="H154" t="s" s="11">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I154" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J154" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K154" s="13"/>
+      <c r="K154" s="10"/>
+      <c r="L154" s="13"/>
     </row>
     <row r="155" ht="22.75" customHeight="1">
       <c r="A155" t="b" s="14">
@@ -7185,23 +7387,24 @@
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
       <c r="D155" t="s" s="16">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E155" s="15"/>
       <c r="F155" s="15"/>
       <c r="G155" t="s" s="16">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="H155" t="s" s="16">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I155" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J155" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K155" s="18"/>
+      <c r="K155" s="15"/>
+      <c r="L155" s="18"/>
     </row>
     <row r="156" ht="22.75" customHeight="1">
       <c r="A156" t="b" s="9">
@@ -7210,23 +7413,24 @@
       <c r="B156" s="10"/>
       <c r="C156" s="10"/>
       <c r="D156" t="s" s="11">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
       <c r="G156" t="s" s="11">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="H156" s="12">
         <v>1</v>
       </c>
       <c r="I156" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J156" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K156" s="13"/>
+      <c r="K156" s="10"/>
+      <c r="L156" s="13"/>
     </row>
     <row r="157" ht="22.75" customHeight="1">
       <c r="A157" t="b" s="14">
@@ -7235,23 +7439,24 @@
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
       <c r="D157" t="s" s="16">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E157" s="15"/>
       <c r="F157" s="15"/>
       <c r="G157" t="s" s="16">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="H157" s="17">
         <v>1</v>
       </c>
       <c r="I157" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J157" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K157" s="18"/>
+      <c r="K157" s="15"/>
+      <c r="L157" s="18"/>
     </row>
     <row r="158" ht="22.75" customHeight="1">
       <c r="A158" t="b" s="9">
@@ -7260,23 +7465,24 @@
       <c r="B158" s="10"/>
       <c r="C158" s="10"/>
       <c r="D158" t="s" s="11">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
       <c r="G158" t="s" s="11">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H158" s="12">
         <v>3</v>
       </c>
       <c r="I158" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J158" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K158" s="13"/>
+      <c r="K158" s="10"/>
+      <c r="L158" s="13"/>
     </row>
     <row r="159" ht="22.75" customHeight="1">
       <c r="A159" t="b" s="14">
@@ -7285,23 +7491,24 @@
       <c r="B159" s="15"/>
       <c r="C159" s="15"/>
       <c r="D159" t="s" s="16">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="E159" s="15"/>
       <c r="F159" s="15"/>
       <c r="G159" t="s" s="16">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="H159" s="17">
         <v>1</v>
       </c>
       <c r="I159" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J159" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K159" s="18"/>
+      <c r="K159" s="15"/>
+      <c r="L159" s="18"/>
     </row>
     <row r="160" ht="22.75" customHeight="1">
       <c r="A160" t="b" s="9">
@@ -7310,23 +7517,24 @@
       <c r="B160" s="10"/>
       <c r="C160" s="10"/>
       <c r="D160" t="s" s="11">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="E160" s="10"/>
       <c r="F160" s="10"/>
       <c r="G160" t="s" s="11">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H160" s="12">
         <v>1</v>
       </c>
       <c r="I160" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J160" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K160" s="13"/>
+      <c r="K160" s="10"/>
+      <c r="L160" s="13"/>
     </row>
     <row r="161" ht="22.75" customHeight="1">
       <c r="A161" t="b" s="14">
@@ -7335,23 +7543,24 @@
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
       <c r="D161" t="s" s="16">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E161" s="15"/>
       <c r="F161" s="15"/>
       <c r="G161" t="s" s="16">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H161" s="17">
         <v>2</v>
       </c>
       <c r="I161" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J161" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K161" s="18"/>
+      <c r="K161" s="15"/>
+      <c r="L161" s="18"/>
     </row>
     <row r="162" ht="22.75" customHeight="1">
       <c r="A162" t="b" s="9">
@@ -7360,23 +7569,24 @@
       <c r="B162" s="10"/>
       <c r="C162" s="10"/>
       <c r="D162" t="s" s="11">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="E162" s="10"/>
       <c r="F162" s="10"/>
       <c r="G162" t="s" s="11">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="H162" s="12">
         <v>4</v>
       </c>
       <c r="I162" t="s" s="11">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="J162" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K162" s="13"/>
+      <c r="K162" s="10"/>
+      <c r="L162" s="13"/>
     </row>
     <row r="163" ht="22.75" customHeight="1">
       <c r="A163" t="b" s="14">
@@ -7385,23 +7595,24 @@
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
       <c r="D163" t="s" s="16">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="E163" s="15"/>
       <c r="F163" s="15"/>
       <c r="G163" t="s" s="16">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H163" s="17">
         <v>4</v>
       </c>
       <c r="I163" t="s" s="16">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="J163" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K163" s="18"/>
+      <c r="K163" s="15"/>
+      <c r="L163" s="18"/>
     </row>
     <row r="164" ht="22.75" customHeight="1">
       <c r="A164" t="b" s="9">
@@ -7410,52 +7621,54 @@
       <c r="B164" s="10"/>
       <c r="C164" s="10"/>
       <c r="D164" t="s" s="11">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
       <c r="G164" t="s" s="11">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="H164" s="12">
         <v>1</v>
       </c>
       <c r="I164" t="s" s="11">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="J164" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K164" s="13"/>
+      <c r="K164" s="10"/>
+      <c r="L164" s="13"/>
     </row>
     <row r="165" ht="50.35" customHeight="1">
       <c r="A165" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B165" t="s" s="16">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C165" s="15"/>
       <c r="D165" t="s" s="16">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E165" t="s" s="19">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F165" s="15"/>
       <c r="G165" t="s" s="16">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="H165" s="17">
         <v>1</v>
       </c>
       <c r="I165" t="s" s="16">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="J165" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K165" s="18"/>
+      <c r="K165" s="15"/>
+      <c r="L165" s="18"/>
     </row>
     <row r="166" ht="22.75" customHeight="1">
       <c r="A166" t="b" s="9">
@@ -7464,12 +7677,12 @@
       <c r="B166" s="10"/>
       <c r="C166" s="10"/>
       <c r="D166" t="s" s="11">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
       <c r="G166" t="s" s="11">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="H166" s="12">
         <v>1</v>
@@ -7478,7 +7691,8 @@
       <c r="J166" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K166" s="13"/>
+      <c r="K166" s="10"/>
+      <c r="L166" s="13"/>
     </row>
     <row r="167" ht="22.75" customHeight="1">
       <c r="A167" t="b" s="14">
@@ -7487,23 +7701,24 @@
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
       <c r="D167" t="s" s="16">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E167" s="15"/>
       <c r="F167" s="15"/>
       <c r="G167" t="s" s="16">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="H167" s="17">
         <v>1</v>
       </c>
       <c r="I167" t="s" s="16">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J167" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K167" s="18"/>
+      <c r="K167" s="15"/>
+      <c r="L167" s="18"/>
     </row>
     <row r="168" ht="22.75" customHeight="1">
       <c r="A168" t="b" s="9">
@@ -7512,23 +7727,24 @@
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
       <c r="D168" t="s" s="11">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
       <c r="G168" t="s" s="11">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="H168" s="12">
         <v>1</v>
       </c>
       <c r="I168" t="s" s="11">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J168" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K168" s="13"/>
+      <c r="K168" s="10"/>
+      <c r="L168" s="13"/>
     </row>
     <row r="169" ht="22.75" customHeight="1">
       <c r="A169" t="b" s="14">
@@ -7537,7 +7753,7 @@
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
       <c r="D169" t="s" s="16">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E169" s="15"/>
       <c r="F169" s="15"/>
@@ -7548,12 +7764,13 @@
         <v>1</v>
       </c>
       <c r="I169" t="s" s="16">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J169" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K169" s="18"/>
+      <c r="K169" s="15"/>
+      <c r="L169" s="18"/>
     </row>
     <row r="170" ht="22.75" customHeight="1">
       <c r="A170" t="b" s="9">
@@ -7562,23 +7779,24 @@
       <c r="B170" s="10"/>
       <c r="C170" s="10"/>
       <c r="D170" t="s" s="11">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
       <c r="G170" t="s" s="11">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H170" s="12">
         <v>1</v>
       </c>
       <c r="I170" t="s" s="11">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J170" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K170" s="13"/>
+      <c r="K170" s="10"/>
+      <c r="L170" s="13"/>
     </row>
     <row r="171" ht="22.75" customHeight="1">
       <c r="A171" t="b" s="14">
@@ -7587,7 +7805,7 @@
       <c r="B171" s="15"/>
       <c r="C171" s="15"/>
       <c r="D171" t="s" s="16">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="E171" s="15"/>
       <c r="F171" s="15"/>
@@ -7598,12 +7816,13 @@
         <v>3</v>
       </c>
       <c r="I171" t="s" s="16">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="J171" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K171" s="18"/>
+      <c r="K171" s="15"/>
+      <c r="L171" s="18"/>
     </row>
     <row r="172" ht="22.75" customHeight="1">
       <c r="A172" t="b" s="9">
@@ -7612,23 +7831,24 @@
       <c r="B172" s="10"/>
       <c r="C172" s="10"/>
       <c r="D172" t="s" s="11">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
       <c r="G172" t="s" s="11">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="H172" s="12">
         <v>41</v>
       </c>
       <c r="I172" t="s" s="11">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="J172" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K172" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K172" s="10"/>
+      <c r="L172" s="13"/>
     </row>
     <row r="173" ht="22.75" customHeight="1">
       <c r="A173" t="b" s="14">
@@ -7637,23 +7857,24 @@
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
       <c r="D173" t="s" s="16">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E173" s="15"/>
       <c r="F173" s="15"/>
       <c r="G173" t="s" s="16">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H173" s="17">
         <v>4</v>
       </c>
       <c r="I173" t="s" s="16">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J173" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K173" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K173" s="15"/>
+      <c r="L173" s="18"/>
     </row>
     <row r="174" ht="22.75" customHeight="1">
       <c r="A174" t="b" s="9">
@@ -7662,23 +7883,24 @@
       <c r="B174" s="10"/>
       <c r="C174" s="10"/>
       <c r="D174" t="s" s="11">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
       <c r="G174" t="s" s="11">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H174" s="12">
         <v>3</v>
       </c>
       <c r="I174" t="s" s="11">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J174" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K174" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K174" s="10"/>
+      <c r="L174" s="13"/>
     </row>
     <row r="175" ht="22.75" customHeight="1">
       <c r="A175" t="b" s="14">
@@ -7687,23 +7909,24 @@
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
       <c r="D175" t="s" s="16">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="E175" s="15"/>
       <c r="F175" s="15"/>
       <c r="G175" t="s" s="16">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="H175" s="17">
         <v>4</v>
       </c>
       <c r="I175" t="s" s="16">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J175" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K175" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K175" s="15"/>
+      <c r="L175" s="18"/>
     </row>
     <row r="176" ht="22.75" customHeight="1">
       <c r="A176" t="b" s="9">
@@ -7712,23 +7935,24 @@
       <c r="B176" s="10"/>
       <c r="C176" s="10"/>
       <c r="D176" t="s" s="11">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="E176" s="10"/>
       <c r="F176" s="10"/>
       <c r="G176" t="s" s="11">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="H176" s="12">
         <v>4</v>
       </c>
       <c r="I176" t="s" s="11">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J176" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K176" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K176" s="10"/>
+      <c r="L176" s="13"/>
     </row>
     <row r="177" ht="22.75" customHeight="1">
       <c r="A177" t="b" s="14">
@@ -7737,23 +7961,24 @@
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
       <c r="D177" t="s" s="16">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="E177" s="15"/>
       <c r="F177" s="15"/>
       <c r="G177" t="s" s="16">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="H177" s="17">
         <v>16</v>
       </c>
       <c r="I177" t="s" s="16">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J177" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K177" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K177" s="15"/>
+      <c r="L177" s="18"/>
     </row>
     <row r="178" ht="22.75" customHeight="1">
       <c r="A178" t="b" s="9">
@@ -7762,23 +7987,24 @@
       <c r="B178" s="10"/>
       <c r="C178" s="10"/>
       <c r="D178" t="s" s="11">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
       <c r="G178" t="s" s="11">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="H178" s="12">
         <v>16</v>
       </c>
       <c r="I178" t="s" s="11">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J178" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K178" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K178" s="10"/>
+      <c r="L178" s="13"/>
     </row>
     <row r="179" ht="22.75" customHeight="1">
       <c r="A179" t="b" s="14">
@@ -7787,37 +8013,38 @@
       <c r="B179" s="15"/>
       <c r="C179" s="15"/>
       <c r="D179" t="s" s="16">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="E179" s="15"/>
       <c r="F179" s="15"/>
       <c r="G179" t="s" s="16">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="H179" s="17">
         <v>3</v>
       </c>
       <c r="I179" t="s" s="16">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="J179" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K179" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K179" s="15"/>
+      <c r="L179" s="18"/>
     </row>
     <row r="180" ht="36.35" customHeight="1">
       <c r="A180" t="b" s="9">
         <v>0</v>
       </c>
       <c r="B180" t="s" s="11">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C180" s="10"/>
       <c r="D180" t="s" s="11">
-        <v>418</v>
-      </c>
-      <c r="E180" t="s" s="23">
-        <v>419</v>
+        <v>426</v>
+      </c>
+      <c r="E180" t="s" s="21">
+        <v>427</v>
       </c>
       <c r="F180" s="10"/>
       <c r="G180" t="s" s="11">
@@ -7830,27 +8057,28 @@
         <v>85</v>
       </c>
       <c r="J180" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K180" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K180" s="10"/>
+      <c r="L180" s="13"/>
     </row>
     <row r="181" ht="22.75" customHeight="1">
       <c r="A181" t="b" s="14">
         <v>0</v>
       </c>
       <c r="B181" t="s" s="16">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C181" s="15"/>
       <c r="D181" t="s" s="16">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="E181" t="s" s="19">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="F181" s="15"/>
       <c r="G181" t="s" s="16">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="H181" s="17">
         <v>1</v>
@@ -7859,9 +8087,10 @@
         <v>85</v>
       </c>
       <c r="J181" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K181" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K181" s="15"/>
+      <c r="L181" s="18"/>
     </row>
     <row r="182" ht="22.75" customHeight="1">
       <c r="A182" t="b" s="9">
@@ -7870,7 +8099,7 @@
       <c r="B182" s="10"/>
       <c r="C182" s="10"/>
       <c r="D182" t="s" s="11">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
@@ -7884,9 +8113,10 @@
         <v>53</v>
       </c>
       <c r="J182" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K182" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K182" s="10"/>
+      <c r="L182" s="13"/>
     </row>
     <row r="183" ht="22.75" customHeight="1">
       <c r="A183" t="b" s="14">
@@ -7895,12 +8125,12 @@
       <c r="B183" s="15"/>
       <c r="C183" s="15"/>
       <c r="D183" t="s" s="16">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="E183" s="15"/>
       <c r="F183" s="15"/>
       <c r="G183" t="s" s="16">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="H183" s="17">
         <v>1</v>
@@ -7909,9 +8139,10 @@
         <v>53</v>
       </c>
       <c r="J183" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K183" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K183" s="15"/>
+      <c r="L183" s="18"/>
     </row>
     <row r="184" ht="36.35" customHeight="1">
       <c r="A184" t="b" s="9">
@@ -7920,14 +8151,14 @@
       <c r="B184" s="10"/>
       <c r="C184" s="10"/>
       <c r="D184" t="s" s="11">
-        <v>427</v>
-      </c>
-      <c r="E184" t="s" s="23">
-        <v>428</v>
+        <v>435</v>
+      </c>
+      <c r="E184" t="s" s="21">
+        <v>436</v>
       </c>
       <c r="F184" s="10"/>
       <c r="G184" t="s" s="11">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="H184" s="12">
         <v>1</v>
@@ -7936,9 +8167,10 @@
         <v>53</v>
       </c>
       <c r="J184" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K184" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K184" s="10"/>
+      <c r="L184" s="13"/>
     </row>
     <row r="185" ht="22.75" customHeight="1">
       <c r="A185" t="b" s="14">
@@ -7947,12 +8179,12 @@
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
       <c r="D185" t="s" s="16">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="E185" s="15"/>
       <c r="F185" s="15"/>
       <c r="G185" t="s" s="16">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H185" s="17">
         <v>15</v>
@@ -7961,9 +8193,10 @@
         <v>53</v>
       </c>
       <c r="J185" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K185" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K185" s="15"/>
+      <c r="L185" s="18"/>
     </row>
     <row r="186" ht="22.75" customHeight="1">
       <c r="A186" t="b" s="9">
@@ -7972,12 +8205,12 @@
       <c r="B186" s="10"/>
       <c r="C186" s="10"/>
       <c r="D186" t="s" s="11">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="E186" s="10"/>
       <c r="F186" s="10"/>
       <c r="G186" t="s" s="11">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="H186" s="12">
         <v>3</v>
@@ -7986,9 +8219,10 @@
         <v>53</v>
       </c>
       <c r="J186" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K186" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K186" s="10"/>
+      <c r="L186" s="13"/>
     </row>
     <row r="187" ht="22.75" customHeight="1">
       <c r="A187" t="b" s="14">
@@ -7997,12 +8231,12 @@
       <c r="B187" s="15"/>
       <c r="C187" s="15"/>
       <c r="D187" t="s" s="16">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="E187" s="15"/>
       <c r="F187" s="15"/>
       <c r="G187" t="s" s="16">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="H187" s="17">
         <v>8</v>
@@ -8011,9 +8245,10 @@
         <v>53</v>
       </c>
       <c r="J187" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K187" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K187" s="15"/>
+      <c r="L187" s="18"/>
     </row>
     <row r="188" ht="22.75" customHeight="1">
       <c r="A188" t="b" s="9">
@@ -8022,23 +8257,24 @@
       <c r="B188" s="10"/>
       <c r="C188" s="10"/>
       <c r="D188" t="s" s="11">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
       <c r="G188" t="s" s="11">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="H188" s="12">
         <v>1</v>
       </c>
       <c r="I188" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J188" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K188" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K188" s="10"/>
+      <c r="L188" s="13"/>
     </row>
     <row r="189" ht="22.75" customHeight="1">
       <c r="A189" t="b" s="14">
@@ -8047,23 +8283,24 @@
       <c r="B189" s="15"/>
       <c r="C189" s="15"/>
       <c r="D189" t="s" s="16">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="E189" s="15"/>
       <c r="F189" s="15"/>
       <c r="G189" t="s" s="16">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="H189" s="17">
         <v>1</v>
       </c>
       <c r="I189" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J189" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K189" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K189" s="15"/>
+      <c r="L189" s="18"/>
     </row>
     <row r="190" ht="22.75" customHeight="1">
       <c r="A190" t="b" s="9">
@@ -8072,23 +8309,24 @@
       <c r="B190" s="10"/>
       <c r="C190" s="10"/>
       <c r="D190" t="s" s="11">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
       <c r="G190" t="s" s="11">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="H190" s="12">
         <v>1</v>
       </c>
       <c r="I190" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J190" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K190" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K190" s="10"/>
+      <c r="L190" s="13"/>
     </row>
     <row r="191" ht="22.75" customHeight="1">
       <c r="A191" t="b" s="14">
@@ -8097,23 +8335,24 @@
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
       <c r="D191" t="s" s="16">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="E191" s="15"/>
       <c r="F191" s="15"/>
       <c r="G191" t="s" s="16">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="H191" s="17">
         <v>3</v>
       </c>
       <c r="I191" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J191" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K191" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K191" s="15"/>
+      <c r="L191" s="18"/>
     </row>
     <row r="192" ht="22.75" customHeight="1">
       <c r="A192" t="b" s="9">
@@ -8122,23 +8361,24 @@
       <c r="B192" s="10"/>
       <c r="C192" s="10"/>
       <c r="D192" t="s" s="11">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
       <c r="G192" t="s" s="11">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H192" s="12">
         <v>2</v>
       </c>
       <c r="I192" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J192" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K192" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K192" s="10"/>
+      <c r="L192" s="13"/>
     </row>
     <row r="193" ht="22.75" customHeight="1">
       <c r="A193" t="b" s="14">
@@ -8147,23 +8387,24 @@
       <c r="B193" s="15"/>
       <c r="C193" s="15"/>
       <c r="D193" t="s" s="16">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="E193" s="15"/>
       <c r="F193" s="15"/>
       <c r="G193" t="s" s="16">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="H193" s="17">
         <v>1</v>
       </c>
       <c r="I193" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J193" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K193" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K193" s="15"/>
+      <c r="L193" s="18"/>
     </row>
     <row r="194" ht="22.75" customHeight="1">
       <c r="A194" t="b" s="9">
@@ -8172,23 +8413,24 @@
       <c r="B194" s="10"/>
       <c r="C194" s="10"/>
       <c r="D194" t="s" s="11">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" t="s" s="11">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="H194" s="12">
         <v>1</v>
       </c>
       <c r="I194" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J194" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K194" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K194" s="10"/>
+      <c r="L194" s="13"/>
     </row>
     <row r="195" ht="22.75" customHeight="1">
       <c r="A195" t="b" s="14">
@@ -8197,23 +8439,24 @@
       <c r="B195" s="15"/>
       <c r="C195" s="15"/>
       <c r="D195" t="s" s="16">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="E195" s="15"/>
       <c r="F195" s="15"/>
       <c r="G195" t="s" s="16">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="H195" s="17">
         <v>1</v>
       </c>
       <c r="I195" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J195" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K195" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K195" s="15"/>
+      <c r="L195" s="18"/>
     </row>
     <row r="196" ht="22.75" customHeight="1">
       <c r="A196" t="b" s="9">
@@ -8222,23 +8465,24 @@
       <c r="B196" s="10"/>
       <c r="C196" s="10"/>
       <c r="D196" t="s" s="11">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
       <c r="G196" t="s" s="11">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="H196" s="12">
         <v>1</v>
       </c>
       <c r="I196" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J196" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K196" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K196" s="10"/>
+      <c r="L196" s="13"/>
     </row>
     <row r="197" ht="22.75" customHeight="1">
       <c r="A197" t="b" s="14">
@@ -8247,23 +8491,24 @@
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
       <c r="D197" t="s" s="16">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="E197" s="15"/>
       <c r="F197" s="15"/>
       <c r="G197" t="s" s="16">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H197" s="17">
         <v>10</v>
       </c>
       <c r="I197" t="s" s="16">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="J197" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K197" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K197" s="15"/>
+      <c r="L197" s="18"/>
     </row>
     <row r="198" ht="22.75" customHeight="1">
       <c r="A198" t="b" s="9">
@@ -8272,23 +8517,24 @@
       <c r="B198" s="10"/>
       <c r="C198" s="10"/>
       <c r="D198" t="s" s="11">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" t="s" s="11">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="H198" s="12">
         <v>1</v>
       </c>
       <c r="I198" t="s" s="11">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="J198" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K198" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K198" s="10"/>
+      <c r="L198" s="13"/>
     </row>
     <row r="199" ht="22.75" customHeight="1">
       <c r="A199" t="b" s="14">
@@ -8297,23 +8543,24 @@
       <c r="B199" s="15"/>
       <c r="C199" s="15"/>
       <c r="D199" t="s" s="16">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E199" s="15"/>
       <c r="F199" s="15"/>
       <c r="G199" t="s" s="16">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="H199" s="17">
         <v>28</v>
       </c>
       <c r="I199" t="s" s="16">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="J199" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K199" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K199" s="15"/>
+      <c r="L199" s="18"/>
     </row>
     <row r="200" ht="22.75" customHeight="1">
       <c r="A200" t="b" s="9">
@@ -8322,23 +8569,24 @@
       <c r="B200" s="10"/>
       <c r="C200" s="10"/>
       <c r="D200" t="s" s="11">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" t="s" s="11">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="H200" s="12">
         <v>1</v>
       </c>
       <c r="I200" t="s" s="11">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="J200" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K200" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K200" s="10"/>
+      <c r="L200" s="13"/>
     </row>
     <row r="201" ht="22.75" customHeight="1">
       <c r="A201" t="b" s="14">
@@ -8347,23 +8595,24 @@
       <c r="B201" s="15"/>
       <c r="C201" s="15"/>
       <c r="D201" t="s" s="16">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E201" s="15"/>
       <c r="F201" s="15"/>
       <c r="G201" t="s" s="16">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="H201" s="17">
         <v>1</v>
       </c>
       <c r="I201" t="s" s="16">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="J201" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K201" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K201" s="15"/>
+      <c r="L201" s="18"/>
     </row>
     <row r="202" ht="22.75" customHeight="1">
       <c r="A202" t="b" s="9">
@@ -8372,12 +8621,12 @@
       <c r="B202" s="10"/>
       <c r="C202" s="10"/>
       <c r="D202" t="s" s="11">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" t="s" s="11">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="H202" s="12">
         <v>1</v>
@@ -8386,9 +8635,10 @@
         <v>53</v>
       </c>
       <c r="J202" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K202" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K202" s="10"/>
+      <c r="L202" s="13"/>
     </row>
     <row r="203" ht="22.75" customHeight="1">
       <c r="A203" t="b" s="14">
@@ -8397,12 +8647,12 @@
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
       <c r="D203" t="s" s="16">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E203" s="15"/>
       <c r="F203" s="15"/>
       <c r="G203" t="s" s="16">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="H203" s="17">
         <v>1</v>
@@ -8411,9 +8661,10 @@
         <v>53</v>
       </c>
       <c r="J203" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K203" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K203" s="15"/>
+      <c r="L203" s="18"/>
     </row>
     <row r="204" ht="22.75" customHeight="1">
       <c r="A204" t="b" s="9">
@@ -8422,12 +8673,12 @@
       <c r="B204" s="10"/>
       <c r="C204" s="10"/>
       <c r="D204" t="s" s="11">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" t="s" s="11">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="H204" s="12">
         <v>1</v>
@@ -8436,9 +8687,10 @@
         <v>53</v>
       </c>
       <c r="J204" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K204" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K204" s="10"/>
+      <c r="L204" s="13"/>
     </row>
     <row r="205" ht="22.75" customHeight="1">
       <c r="A205" t="b" s="14">
@@ -8447,12 +8699,12 @@
       <c r="B205" s="15"/>
       <c r="C205" s="15"/>
       <c r="D205" t="s" s="16">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E205" s="15"/>
       <c r="F205" s="15"/>
       <c r="G205" t="s" s="16">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="H205" s="17">
         <v>8</v>
@@ -8461,9 +8713,10 @@
         <v>53</v>
       </c>
       <c r="J205" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K205" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K205" s="15"/>
+      <c r="L205" s="18"/>
     </row>
     <row r="206" ht="22.75" customHeight="1">
       <c r="A206" t="b" s="9">
@@ -8472,12 +8725,12 @@
       <c r="B206" s="10"/>
       <c r="C206" s="10"/>
       <c r="D206" t="s" s="11">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" t="s" s="11">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="H206" s="12">
         <v>3</v>
@@ -8486,9 +8739,10 @@
         <v>53</v>
       </c>
       <c r="J206" t="s" s="11">
-        <v>401</v>
-      </c>
-      <c r="K206" s="13"/>
+        <v>409</v>
+      </c>
+      <c r="K206" s="10"/>
+      <c r="L206" s="13"/>
     </row>
     <row r="207" ht="22.75" customHeight="1">
       <c r="A207" t="b" s="14">
@@ -8497,12 +8751,12 @@
       <c r="B207" s="15"/>
       <c r="C207" s="15"/>
       <c r="D207" t="s" s="16">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E207" s="15"/>
       <c r="F207" s="15"/>
       <c r="G207" t="s" s="16">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="H207" s="17">
         <v>3</v>
@@ -8511,9 +8765,10 @@
         <v>53</v>
       </c>
       <c r="J207" t="s" s="16">
-        <v>401</v>
-      </c>
-      <c r="K207" s="18"/>
+        <v>409</v>
+      </c>
+      <c r="K207" s="15"/>
+      <c r="L207" s="18"/>
     </row>
     <row r="208" ht="22.75" customHeight="1">
       <c r="A208" t="b" s="9">
@@ -8522,12 +8777,12 @@
       <c r="B208" s="10"/>
       <c r="C208" s="10"/>
       <c r="D208" t="s" s="11">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" t="s" s="11">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H208" s="12">
         <v>16</v>
@@ -8536,9 +8791,10 @@
         <v>53</v>
       </c>
       <c r="J208" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K208" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K208" s="10"/>
+      <c r="L208" s="13"/>
     </row>
     <row r="209" ht="22.75" customHeight="1">
       <c r="A209" t="b" s="14">
@@ -8547,12 +8803,12 @@
       <c r="B209" s="15"/>
       <c r="C209" s="15"/>
       <c r="D209" t="s" s="16">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E209" s="15"/>
       <c r="F209" s="15"/>
       <c r="G209" t="s" s="16">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H209" s="17">
         <v>2</v>
@@ -8561,9 +8817,10 @@
         <v>53</v>
       </c>
       <c r="J209" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K209" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K209" s="15"/>
+      <c r="L209" s="18"/>
     </row>
     <row r="210" ht="22.75" customHeight="1">
       <c r="A210" t="b" s="9">
@@ -8572,12 +8829,12 @@
       <c r="B210" s="10"/>
       <c r="C210" s="10"/>
       <c r="D210" t="s" s="11">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" t="s" s="11">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="H210" s="12">
         <v>4</v>
@@ -8586,9 +8843,10 @@
         <v>53</v>
       </c>
       <c r="J210" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K210" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K210" s="10"/>
+      <c r="L210" s="13"/>
     </row>
     <row r="211" ht="22.75" customHeight="1">
       <c r="A211" t="b" s="14">
@@ -8597,12 +8855,12 @@
       <c r="B211" s="15"/>
       <c r="C211" s="15"/>
       <c r="D211" t="s" s="16">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E211" s="15"/>
       <c r="F211" s="15"/>
       <c r="G211" t="s" s="16">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="H211" s="17">
         <v>4</v>
@@ -8611,9 +8869,10 @@
         <v>53</v>
       </c>
       <c r="J211" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K211" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K211" s="15"/>
+      <c r="L211" s="18"/>
     </row>
     <row r="212" ht="22.75" customHeight="1">
       <c r="A212" t="b" s="9">
@@ -8622,12 +8881,12 @@
       <c r="B212" s="10"/>
       <c r="C212" s="10"/>
       <c r="D212" t="s" s="11">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" t="s" s="11">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="H212" s="12">
         <v>3</v>
@@ -8636,9 +8895,10 @@
         <v>53</v>
       </c>
       <c r="J212" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K212" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K212" s="10"/>
+      <c r="L212" s="13"/>
     </row>
     <row r="213" ht="22.75" customHeight="1">
       <c r="A213" t="b" s="14">
@@ -8647,12 +8907,12 @@
       <c r="B213" s="15"/>
       <c r="C213" s="15"/>
       <c r="D213" t="s" s="16">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="E213" s="15"/>
       <c r="F213" s="15"/>
       <c r="G213" t="s" s="16">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="H213" s="17">
         <v>13</v>
@@ -8661,9 +8921,10 @@
         <v>53</v>
       </c>
       <c r="J213" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K213" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K213" s="15"/>
+      <c r="L213" s="18"/>
     </row>
     <row r="214" ht="22.75" customHeight="1">
       <c r="A214" t="b" s="9">
@@ -8672,12 +8933,12 @@
       <c r="B214" s="10"/>
       <c r="C214" s="10"/>
       <c r="D214" t="s" s="11">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" t="s" s="11">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="H214" s="12">
         <v>12</v>
@@ -8686,9 +8947,10 @@
         <v>53</v>
       </c>
       <c r="J214" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K214" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K214" s="10"/>
+      <c r="L214" s="13"/>
     </row>
     <row r="215" ht="22.75" customHeight="1">
       <c r="A215" t="b" s="14">
@@ -8697,12 +8959,12 @@
       <c r="B215" s="15"/>
       <c r="C215" s="15"/>
       <c r="D215" t="s" s="16">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="E215" s="15"/>
       <c r="F215" s="15"/>
       <c r="G215" t="s" s="16">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="H215" s="17">
         <v>8</v>
@@ -8711,9 +8973,10 @@
         <v>53</v>
       </c>
       <c r="J215" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K215" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K215" s="15"/>
+      <c r="L215" s="18"/>
     </row>
     <row r="216" ht="22.75" customHeight="1">
       <c r="A216" t="b" s="9">
@@ -8722,12 +8985,12 @@
       <c r="B216" s="10"/>
       <c r="C216" s="10"/>
       <c r="D216" t="s" s="11">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
       <c r="G216" t="s" s="11">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="H216" s="12">
         <v>16</v>
@@ -8736,9 +8999,10 @@
         <v>53</v>
       </c>
       <c r="J216" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K216" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K216" s="10"/>
+      <c r="L216" s="13"/>
     </row>
     <row r="217" ht="22.75" customHeight="1">
       <c r="A217" t="b" s="14">
@@ -8747,12 +9011,12 @@
       <c r="B217" s="15"/>
       <c r="C217" s="15"/>
       <c r="D217" t="s" s="16">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="E217" s="15"/>
       <c r="F217" s="15"/>
       <c r="G217" t="s" s="16">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="H217" s="17">
         <v>1</v>
@@ -8761,9 +9025,10 @@
         <v>53</v>
       </c>
       <c r="J217" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K217" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K217" s="15"/>
+      <c r="L217" s="18"/>
     </row>
     <row r="218" ht="22.75" customHeight="1">
       <c r="A218" t="b" s="9">
@@ -8772,12 +9037,12 @@
       <c r="B218" s="10"/>
       <c r="C218" s="10"/>
       <c r="D218" t="s" s="11">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
       <c r="G218" t="s" s="11">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="H218" s="12">
         <v>1</v>
@@ -8786,9 +9051,10 @@
         <v>53</v>
       </c>
       <c r="J218" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K218" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K218" s="10"/>
+      <c r="L218" s="13"/>
     </row>
     <row r="219" ht="22.75" customHeight="1">
       <c r="A219" t="b" s="14">
@@ -8797,12 +9063,12 @@
       <c r="B219" s="15"/>
       <c r="C219" s="15"/>
       <c r="D219" t="s" s="16">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="E219" s="15"/>
       <c r="F219" s="15"/>
       <c r="G219" t="s" s="16">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="H219" s="17">
         <v>1</v>
@@ -8811,9 +9077,10 @@
         <v>53</v>
       </c>
       <c r="J219" t="s" s="16">
-        <v>456</v>
-      </c>
-      <c r="K219" s="18"/>
+        <v>464</v>
+      </c>
+      <c r="K219" s="15"/>
+      <c r="L219" s="18"/>
     </row>
     <row r="220" ht="22.75" customHeight="1">
       <c r="A220" t="b" s="9">
@@ -8822,12 +9089,12 @@
       <c r="B220" s="10"/>
       <c r="C220" s="10"/>
       <c r="D220" t="s" s="11">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
       <c r="G220" t="s" s="11">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="H220" s="12">
         <v>1</v>
@@ -8836,9 +9103,10 @@
         <v>53</v>
       </c>
       <c r="J220" t="s" s="11">
-        <v>456</v>
-      </c>
-      <c r="K220" s="13"/>
+        <v>464</v>
+      </c>
+      <c r="K220" s="10"/>
+      <c r="L220" s="13"/>
     </row>
     <row r="221" ht="22.75" customHeight="1">
       <c r="A221" t="b" s="14">
@@ -8847,23 +9115,24 @@
       <c r="B221" s="15"/>
       <c r="C221" s="15"/>
       <c r="D221" t="s" s="16">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="E221" s="15"/>
       <c r="F221" s="15"/>
       <c r="G221" t="s" s="16">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="H221" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I221" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J221" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K221" s="18"/>
+      <c r="K221" s="15"/>
+      <c r="L221" s="18"/>
     </row>
     <row r="222" ht="22.75" customHeight="1">
       <c r="A222" t="b" s="9">
@@ -8872,23 +9141,24 @@
       <c r="B222" s="10"/>
       <c r="C222" s="10"/>
       <c r="D222" t="s" s="11">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
       <c r="G222" t="s" s="11">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="H222" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I222" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J222" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K222" s="13"/>
+      <c r="K222" s="10"/>
+      <c r="L222" s="13"/>
     </row>
     <row r="223" ht="22.75" customHeight="1">
       <c r="A223" t="b" s="14">
@@ -8897,23 +9167,24 @@
       <c r="B223" s="15"/>
       <c r="C223" s="15"/>
       <c r="D223" t="s" s="16">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E223" s="15"/>
       <c r="F223" s="15"/>
       <c r="G223" t="s" s="16">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="H223" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I223" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J223" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K223" s="18"/>
+      <c r="K223" s="15"/>
+      <c r="L223" s="18"/>
     </row>
     <row r="224" ht="22.75" customHeight="1">
       <c r="A224" t="b" s="9">
@@ -8922,23 +9193,24 @@
       <c r="B224" s="10"/>
       <c r="C224" s="10"/>
       <c r="D224" t="s" s="11">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
       <c r="G224" t="s" s="11">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="H224" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I224" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J224" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K224" s="13"/>
+      <c r="K224" s="10"/>
+      <c r="L224" s="13"/>
     </row>
     <row r="225" ht="22.75" customHeight="1">
       <c r="A225" t="b" s="14">
@@ -8947,23 +9219,24 @@
       <c r="B225" s="15"/>
       <c r="C225" s="15"/>
       <c r="D225" t="s" s="16">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E225" s="15"/>
       <c r="F225" s="15"/>
       <c r="G225" t="s" s="16">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="H225" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I225" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J225" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K225" s="18"/>
+      <c r="K225" s="15"/>
+      <c r="L225" s="18"/>
     </row>
     <row r="226" ht="22.75" customHeight="1">
       <c r="A226" t="b" s="9">
@@ -8972,23 +9245,24 @@
       <c r="B226" s="10"/>
       <c r="C226" s="10"/>
       <c r="D226" t="s" s="11">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
       <c r="G226" t="s" s="11">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="H226" t="s" s="11">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="I226" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J226" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K226" s="13"/>
+      <c r="K226" s="10"/>
+      <c r="L226" s="13"/>
     </row>
     <row r="227" ht="22.75" customHeight="1">
       <c r="A227" t="b" s="14">
@@ -8997,23 +9271,24 @@
       <c r="B227" s="15"/>
       <c r="C227" s="15"/>
       <c r="D227" t="s" s="16">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="E227" s="15"/>
       <c r="F227" s="15"/>
       <c r="G227" t="s" s="16">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="H227" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I227" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J227" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K227" s="18"/>
+      <c r="K227" s="15"/>
+      <c r="L227" s="18"/>
     </row>
     <row r="228" ht="22.75" customHeight="1">
       <c r="A228" t="b" s="9">
@@ -9022,23 +9297,24 @@
       <c r="B228" s="10"/>
       <c r="C228" s="10"/>
       <c r="D228" t="s" s="11">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
       <c r="G228" t="s" s="11">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="H228" s="12">
         <v>1</v>
       </c>
       <c r="I228" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J228" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K228" s="13"/>
+      <c r="K228" s="10"/>
+      <c r="L228" s="13"/>
     </row>
     <row r="229" ht="22.75" customHeight="1">
       <c r="A229" t="b" s="14">
@@ -9047,23 +9323,24 @@
       <c r="B229" s="15"/>
       <c r="C229" s="15"/>
       <c r="D229" t="s" s="16">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="E229" s="15"/>
       <c r="F229" s="15"/>
       <c r="G229" t="s" s="16">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="H229" s="17">
         <v>1</v>
       </c>
       <c r="I229" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J229" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K229" s="18"/>
+      <c r="K229" s="15"/>
+      <c r="L229" s="18"/>
     </row>
     <row r="230" ht="22.75" customHeight="1">
       <c r="A230" t="b" s="9">
@@ -9072,23 +9349,24 @@
       <c r="B230" s="10"/>
       <c r="C230" s="10"/>
       <c r="D230" t="s" s="11">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
       <c r="G230" t="s" s="11">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="H230" s="12">
         <v>1</v>
       </c>
       <c r="I230" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J230" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K230" s="13"/>
+      <c r="K230" s="10"/>
+      <c r="L230" s="13"/>
     </row>
     <row r="231" ht="22.75" customHeight="1">
       <c r="A231" t="b" s="14">
@@ -9097,23 +9375,24 @@
       <c r="B231" s="15"/>
       <c r="C231" s="15"/>
       <c r="D231" t="s" s="16">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E231" s="15"/>
       <c r="F231" s="15"/>
       <c r="G231" t="s" s="16">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="H231" s="17">
         <v>1</v>
       </c>
       <c r="I231" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J231" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K231" s="18"/>
+      <c r="K231" s="15"/>
+      <c r="L231" s="18"/>
     </row>
     <row r="232" ht="22.75" customHeight="1">
       <c r="A232" t="b" s="9">
@@ -9122,23 +9401,24 @@
       <c r="B232" s="10"/>
       <c r="C232" s="10"/>
       <c r="D232" t="s" s="11">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
       <c r="G232" t="s" s="11">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="H232" s="12">
         <v>0</v>
       </c>
       <c r="I232" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J232" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K232" s="13"/>
+      <c r="K232" s="10"/>
+      <c r="L232" s="13"/>
     </row>
     <row r="233" ht="22.75" customHeight="1">
       <c r="A233" t="b" s="14">
@@ -9147,23 +9427,24 @@
       <c r="B233" s="15"/>
       <c r="C233" s="15"/>
       <c r="D233" t="s" s="16">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E233" s="15"/>
       <c r="F233" s="15"/>
       <c r="G233" t="s" s="16">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="H233" s="17">
         <v>0</v>
       </c>
       <c r="I233" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J233" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K233" s="18"/>
+      <c r="K233" s="15"/>
+      <c r="L233" s="18"/>
     </row>
     <row r="234" ht="22.75" customHeight="1">
       <c r="A234" t="b" s="9">
@@ -9172,23 +9453,24 @@
       <c r="B234" s="10"/>
       <c r="C234" s="10"/>
       <c r="D234" t="s" s="11">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
       <c r="G234" t="s" s="11">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="H234" s="12">
         <v>1</v>
       </c>
       <c r="I234" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J234" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K234" s="13"/>
+      <c r="K234" s="10"/>
+      <c r="L234" s="13"/>
     </row>
     <row r="235" ht="22.75" customHeight="1">
       <c r="A235" t="b" s="14">
@@ -9197,23 +9479,24 @@
       <c r="B235" s="15"/>
       <c r="C235" s="15"/>
       <c r="D235" t="s" s="16">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E235" s="15"/>
       <c r="F235" s="15"/>
       <c r="G235" t="s" s="16">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="H235" s="17">
         <v>1</v>
       </c>
       <c r="I235" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J235" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K235" s="18"/>
+      <c r="K235" s="15"/>
+      <c r="L235" s="18"/>
     </row>
     <row r="236" ht="22.75" customHeight="1">
       <c r="A236" t="b" s="9">
@@ -9222,23 +9505,24 @@
       <c r="B236" s="10"/>
       <c r="C236" s="10"/>
       <c r="D236" t="s" s="11">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
       <c r="G236" t="s" s="11">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="H236" s="12">
         <v>0</v>
       </c>
       <c r="I236" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J236" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K236" s="13"/>
+      <c r="K236" s="10"/>
+      <c r="L236" s="13"/>
     </row>
     <row r="237" ht="22.75" customHeight="1">
       <c r="A237" t="b" s="14">
@@ -9247,23 +9531,24 @@
       <c r="B237" s="15"/>
       <c r="C237" s="15"/>
       <c r="D237" t="s" s="16">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="E237" s="15"/>
       <c r="F237" s="15"/>
       <c r="G237" t="s" s="16">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="H237" s="17">
         <v>1</v>
       </c>
       <c r="I237" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J237" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K237" s="18"/>
+      <c r="K237" s="15"/>
+      <c r="L237" s="18"/>
     </row>
     <row r="238" ht="22.75" customHeight="1">
       <c r="A238" t="b" s="9">
@@ -9272,23 +9557,24 @@
       <c r="B238" s="10"/>
       <c r="C238" s="10"/>
       <c r="D238" t="s" s="11">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
       <c r="G238" t="s" s="11">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="H238" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I238" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J238" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K238" s="13"/>
+      <c r="K238" s="10"/>
+      <c r="L238" s="13"/>
     </row>
     <row r="239" ht="22.75" customHeight="1">
       <c r="A239" t="b" s="14">
@@ -9297,23 +9583,24 @@
       <c r="B239" s="15"/>
       <c r="C239" s="15"/>
       <c r="D239" t="s" s="16">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E239" s="15"/>
       <c r="F239" s="15"/>
       <c r="G239" t="s" s="16">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="H239" t="s" s="16">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I239" t="s" s="16">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J239" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="K239" s="18"/>
+      <c r="K239" s="15"/>
+      <c r="L239" s="18"/>
     </row>
     <row r="240" ht="22.75" customHeight="1">
       <c r="A240" t="b" s="9">
@@ -9322,23 +9609,24 @@
       <c r="B240" s="10"/>
       <c r="C240" s="10"/>
       <c r="D240" t="s" s="11">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
       <c r="G240" t="s" s="11">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="H240" t="s" s="11">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="I240" t="s" s="11">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="J240" t="s" s="11">
         <v>11</v>
       </c>
-      <c r="K240" s="13"/>
+      <c r="K240" s="10"/>
+      <c r="L240" s="13"/>
     </row>
     <row r="241" ht="22.75" customHeight="1">
       <c r="A241" t="b" s="14">
@@ -9353,7 +9641,8 @@
       <c r="H241" s="26"/>
       <c r="I241" s="26"/>
       <c r="J241" s="26"/>
-      <c r="K241" s="27"/>
+      <c r="K241" s="26"/>
+      <c r="L241" s="27"/>
     </row>
     <row r="242" ht="22.75" customHeight="1">
       <c r="A242" t="b" s="9">
@@ -9368,7 +9657,8 @@
       <c r="H242" s="29"/>
       <c r="I242" s="29"/>
       <c r="J242" s="29"/>
-      <c r="K242" s="30"/>
+      <c r="K242" s="29"/>
+      <c r="L242" s="30"/>
     </row>
     <row r="243" ht="22.75" customHeight="1">
       <c r="A243" t="b" s="14">
@@ -9383,7 +9673,8 @@
       <c r="H243" s="26"/>
       <c r="I243" s="26"/>
       <c r="J243" s="26"/>
-      <c r="K243" s="27"/>
+      <c r="K243" s="26"/>
+      <c r="L243" s="27"/>
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" t="b" s="31">
@@ -9398,22 +9689,27 @@
       <c r="H244" s="34"/>
       <c r="I244" s="34"/>
       <c r="J244" s="34"/>
-      <c r="K244" s="35"/>
+      <c r="K244" s="34"/>
+      <c r="L244" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F45" r:id="rId1" location="" tooltip="" display="https://www.ebay.nl/itm/124591812891?hash=item1d0240311b:g:hhQAAOSwKThgNhUA"/>
-    <hyperlink ref="F55" r:id="rId2" location="" tooltip="" display="https://www.ebay.com/itm/283869354793?hash=item4217ee9b29:g:DoAAAOSwoA5dVDuM"/>
-    <hyperlink ref="F56" r:id="rId3" location="" tooltip="" display="https://www.ebay.nl/itm/333851303960?hash=item4dbb16a018:g:cqkAAOSwgVZfdfXU"/>
-    <hyperlink ref="F59" r:id="rId4" location="" tooltip="" display="https://www.ebay.com/itm/133263821487?hash=item1f07248aaf:g:vTYAAOSw2h1d6pzg"/>
-    <hyperlink ref="F61" r:id="rId5" location="" tooltip="" display="https://www.ebay.com/itm/133266092659?hash=item1f07473273:g:6~QAAOSwczxd7VLI"/>
-    <hyperlink ref="F63" r:id="rId6" location="" tooltip="" display="https://www.ebay.nl/itm/164312001976?hash=item2641c22db8:g:JlsAAOSwZxNfAY7L"/>
-    <hyperlink ref="F66" r:id="rId7" location="" tooltip="" display="https://www.budgetronics.eu/nl/ics/microcontrollers/z80a-cpu/a-10778-10000143"/>
-    <hyperlink ref="F67" r:id="rId8" location="" tooltip="" display="https://www.ebay.com/itm/224418751517"/>
-    <hyperlink ref="F68" r:id="rId9" location="" tooltip="" display="https://www.ebay.com/itm/353533557328?hash=item52503dfa50:g:yRoAAOSw919gxnee"/>
+    <hyperlink ref="F51" r:id="rId2" location="" tooltip="" display="https://www.eprelectronics.com/store/E-mu-Drum-machine-Command-Station-PARTS/E-mu-SP-1200-Sampling-Percussion-Model-7030-/IC-MDAC-AD7523-p62.html"/>
+    <hyperlink ref="F55" r:id="rId3" location="" tooltip="" display="https://www.ebay.com/itm/283869354793?hash=item4217ee9b29:g:DoAAAOSwoA5dVDuM"/>
+    <hyperlink ref="F56" r:id="rId4" location="" tooltip="" display="https://www.ebay.nl/itm/333851303960?hash=item4dbb16a018:g:cqkAAOSwgVZfdfXU"/>
+    <hyperlink ref="F59" r:id="rId5" location="" tooltip="" display="https://syntaur.com/Part-6666-ic-e-mu-ip357-sp1200-z80-ram-pal"/>
+    <hyperlink ref="L59" r:id="rId6" location="" tooltip="" display="https://www.ebay.nl/sch/i.html?_nkw=PAL12H6CN+&amp;_sacat=0&amp;_from=R40&amp;_trksid=m570.l1313"/>
+    <hyperlink ref="F60" r:id="rId7" location="" tooltip="" display="https://syntaur.com/Part-6797-ic-e-mu-ip358-sp-1200-chip-select-pal"/>
+    <hyperlink ref="L61" r:id="rId8" location="" tooltip="" display="https://www.ebay.com/itm/133266092659?hash=item1f07473273:g:6~QAAOSwczxd7VLI"/>
+    <hyperlink ref="F63" r:id="rId9" location="" tooltip="" display="https://www.ebay.nl/itm/164312001976?hash=item2641c22db8:g:JlsAAOSwZxNfAY7L"/>
+    <hyperlink ref="F66" r:id="rId10" location="" tooltip="" display="https://www.budgetronics.eu/nl/ics/microcontrollers/z80a-cpu/a-10778-10000143"/>
+    <hyperlink ref="F67" r:id="rId11" location="" tooltip="" display="https://www.ebay.com/itm/224418751517"/>
+    <hyperlink ref="F68" r:id="rId12" location="" tooltip="" display="https://www.ebay.com/itm/353533557328?hash=item52503dfa50:g:yRoAAOSw919gxnee"/>
+    <hyperlink ref="F92" r:id="rId13" location="" tooltip="" display="https://www.ebay.nl/itm/225089491745?hash=item3468611321:g:UCkAAOSwmLlX2BrS&amp;amdata=enc:AQAIAAAA4MXkkTgkr469mE2jv47jaZSFkmu1KXiQnX/Nso3mcPS97IzzypAk0H+o9rlIYDpmkjyBVGYOWBtZtoT+BdeHSUU6AGFDY3SfO/YE5PuEZfCLTM4odbubofQn0JgDGTHJC6/TlEpXOjxiXHQ0OqXJztKbwwp+TFjcAtefcxbLPRNhiOoebneGfvAvEsmtcfkoqWswQudfCdiVs+C5iNOrlAA634r3DxrBAWRFFXCnr1TsvKrWbRQ36GYl1kbaPU04P1jLsqCYglIlL0cKuBR4R9uCn02Mzmm5JRSdt5+aJNYf|tkp:BFBM0oLsq9Vi"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.25" bottom="0.25" header="0.25" footer="0.25"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
